--- a/compare/output/dscale_RenTES_downscaled_SSP126.xlsx
+++ b/compare/output/dscale_RenTES_downscaled_SSP126.xlsx
@@ -526,58 +526,58 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>453591.449683</v>
+        <v>453478.049984</v>
       </c>
       <c r="F2" t="n">
-        <v>467286.930992</v>
+        <v>467073.086906</v>
       </c>
       <c r="G2" t="n">
-        <v>546659.4480720001</v>
+        <v>546312.104264</v>
       </c>
       <c r="H2" t="n">
-        <v>663050.608308</v>
+        <v>662527.280919</v>
       </c>
       <c r="I2" t="n">
-        <v>833710.339845</v>
+        <v>832940.843798</v>
       </c>
       <c r="J2" t="n">
-        <v>1088089.389538</v>
+        <v>1086958.900602</v>
       </c>
       <c r="K2" t="n">
-        <v>1371576.546568</v>
+        <v>1370008.094963</v>
       </c>
       <c r="L2" t="n">
-        <v>1710731.346795</v>
+        <v>1708605.68483</v>
       </c>
       <c r="M2" t="n">
-        <v>2117616.997925</v>
+        <v>2114770.255817</v>
       </c>
       <c r="N2" t="n">
-        <v>2594114.079296</v>
+        <v>2590340.877735</v>
       </c>
       <c r="O2" t="n">
-        <v>3077429.915175</v>
+        <v>3072578.191526</v>
       </c>
       <c r="P2" t="n">
-        <v>3529405.358609</v>
+        <v>3523354.928468</v>
       </c>
       <c r="Q2" t="n">
-        <v>3885098.705953</v>
+        <v>3877824.820174</v>
       </c>
       <c r="R2" t="n">
-        <v>4131292.744573</v>
+        <v>4122761.639741</v>
       </c>
       <c r="S2" t="n">
-        <v>4273894.839155</v>
+        <v>4264010.922458</v>
       </c>
       <c r="T2" t="n">
-        <v>4352378.772525</v>
+        <v>4340850.510851</v>
       </c>
       <c r="U2" t="n">
-        <v>4466978.571419</v>
+        <v>4453035.735657</v>
       </c>
       <c r="V2" t="n">
-        <v>4573606.898899</v>
+        <v>4556089.704933</v>
       </c>
     </row>
     <row r="3">
@@ -602,58 +602,58 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38279.851226</v>
+        <v>38271.18871</v>
       </c>
       <c r="F3" t="n">
-        <v>35009.952897</v>
+        <v>34995.660602</v>
       </c>
       <c r="G3" t="n">
-        <v>38537.852404</v>
+        <v>38516.068817</v>
       </c>
       <c r="H3" t="n">
-        <v>46186.741775</v>
+        <v>46154.204432</v>
       </c>
       <c r="I3" t="n">
-        <v>58592.943526</v>
+        <v>58544.399021</v>
       </c>
       <c r="J3" t="n">
-        <v>78398.714968</v>
+        <v>78324.936347</v>
       </c>
       <c r="K3" t="n">
-        <v>101563.285713</v>
+        <v>101456.962195</v>
       </c>
       <c r="L3" t="n">
-        <v>127693.314473</v>
+        <v>127546.869892</v>
       </c>
       <c r="M3" t="n">
-        <v>153709.006518</v>
+        <v>153517.868936</v>
       </c>
       <c r="N3" t="n">
-        <v>175395.109674</v>
+        <v>175160.356209</v>
       </c>
       <c r="O3" t="n">
-        <v>190045.942487</v>
+        <v>189772.69052</v>
       </c>
       <c r="P3" t="n">
-        <v>198351.677743</v>
+        <v>198044.659596</v>
       </c>
       <c r="Q3" t="n">
-        <v>200415.049402</v>
+        <v>200079.481387</v>
       </c>
       <c r="R3" t="n">
-        <v>197648.816188</v>
+        <v>197287.068467</v>
       </c>
       <c r="S3" t="n">
-        <v>191525.346564</v>
+        <v>191136.001482</v>
       </c>
       <c r="T3" t="n">
-        <v>183990.266973</v>
+        <v>183565.121642</v>
       </c>
       <c r="U3" t="n">
-        <v>175265.957429</v>
+        <v>174793.436227</v>
       </c>
       <c r="V3" t="n">
-        <v>165991.641001</v>
+        <v>165448.383386</v>
       </c>
     </row>
     <row r="4">
@@ -678,58 +678,58 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45577.434674</v>
+        <v>45568.527716</v>
       </c>
       <c r="F4" t="n">
-        <v>35882.488511</v>
+        <v>35870.651133</v>
       </c>
       <c r="G4" t="n">
-        <v>33391.505011</v>
+        <v>33377.385433</v>
       </c>
       <c r="H4" t="n">
-        <v>35452.984431</v>
+        <v>35435.372706</v>
       </c>
       <c r="I4" t="n">
-        <v>41323.268983</v>
+        <v>41300.144966</v>
       </c>
       <c r="J4" t="n">
-        <v>51457.662515</v>
+        <v>51426.098739</v>
       </c>
       <c r="K4" t="n">
-        <v>62516.990256</v>
+        <v>62475.601829</v>
       </c>
       <c r="L4" t="n">
-        <v>74463.604265</v>
+        <v>74410.970871</v>
       </c>
       <c r="M4" t="n">
-        <v>86667.739493</v>
+        <v>86602.515235</v>
       </c>
       <c r="N4" t="n">
-        <v>98290.559165</v>
+        <v>98211.719708</v>
       </c>
       <c r="O4" t="n">
-        <v>107323.795162</v>
+        <v>107231.74834</v>
       </c>
       <c r="P4" t="n">
-        <v>113628.228745</v>
+        <v>113523.602937</v>
       </c>
       <c r="Q4" t="n">
-        <v>116538.319843</v>
+        <v>116422.838719</v>
       </c>
       <c r="R4" t="n">
-        <v>116884.547942</v>
+        <v>116758.716002</v>
       </c>
       <c r="S4" t="n">
-        <v>117532.895883</v>
+        <v>117391.344859</v>
       </c>
       <c r="T4" t="n">
-        <v>118158.267655</v>
+        <v>117994.262805</v>
       </c>
       <c r="U4" t="n">
-        <v>117198.993242</v>
+        <v>117007.644915</v>
       </c>
       <c r="V4" t="n">
-        <v>113769.65162</v>
+        <v>113544.892056</v>
       </c>
     </row>
     <row r="5">
@@ -754,58 +754,58 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21745.351765</v>
+        <v>21757.972247</v>
       </c>
       <c r="F5" t="n">
-        <v>25104.982268</v>
+        <v>25129.001532</v>
       </c>
       <c r="G5" t="n">
-        <v>36260.185122</v>
+        <v>36299.058973</v>
       </c>
       <c r="H5" t="n">
-        <v>52911.645599</v>
+        <v>52970.807575</v>
       </c>
       <c r="I5" t="n">
-        <v>75137.249624</v>
+        <v>75226.393199</v>
       </c>
       <c r="J5" t="n">
-        <v>104444.655676</v>
+        <v>104580.296935</v>
       </c>
       <c r="K5" t="n">
-        <v>134607.742973</v>
+        <v>134801.523705</v>
       </c>
       <c r="L5" t="n">
-        <v>166504.674635</v>
+        <v>166768.845942</v>
       </c>
       <c r="M5" t="n">
-        <v>199433.293022</v>
+        <v>199778.711564</v>
       </c>
       <c r="N5" t="n">
-        <v>231541.781442</v>
+        <v>231977.221766</v>
       </c>
       <c r="O5" t="n">
-        <v>257002.090634</v>
+        <v>257527.830467</v>
       </c>
       <c r="P5" t="n">
-        <v>274490.990282</v>
+        <v>275107.38385</v>
       </c>
       <c r="Q5" t="n">
-        <v>282714.01869</v>
+        <v>283421.034831</v>
       </c>
       <c r="R5" t="n">
-        <v>285123.243474</v>
+        <v>285926.022603</v>
       </c>
       <c r="S5" t="n">
-        <v>289374.247648</v>
+        <v>290284.43013</v>
       </c>
       <c r="T5" t="n">
-        <v>295053.039833</v>
+        <v>296096.327501</v>
       </c>
       <c r="U5" t="n">
-        <v>298022.18004</v>
+        <v>299242.082016</v>
       </c>
       <c r="V5" t="n">
-        <v>295757.84295</v>
+        <v>297228.775699</v>
       </c>
     </row>
     <row r="6">
@@ -830,58 +830,58 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1152248.317399</v>
+        <v>1152244.203751</v>
       </c>
       <c r="F6" t="n">
-        <v>1157150.569453</v>
+        <v>1157144.07797</v>
       </c>
       <c r="G6" t="n">
-        <v>1208184.009919</v>
+        <v>1208221.274175</v>
       </c>
       <c r="H6" t="n">
-        <v>1335962.682251</v>
+        <v>1336085.063336</v>
       </c>
       <c r="I6" t="n">
-        <v>1597273.033576</v>
+        <v>1597516.305782</v>
       </c>
       <c r="J6" t="n">
-        <v>2037878.772902</v>
+        <v>2038297.645105</v>
       </c>
       <c r="K6" t="n">
-        <v>2552604.203867</v>
+        <v>2553227.39675</v>
       </c>
       <c r="L6" t="n">
-        <v>3139918.836251</v>
+        <v>3140778.684161</v>
       </c>
       <c r="M6" t="n">
-        <v>3782757.084298</v>
+        <v>3783866.97337</v>
       </c>
       <c r="N6" t="n">
-        <v>4445068.62688</v>
+        <v>4446423.39551</v>
       </c>
       <c r="O6" t="n">
-        <v>5026478.641585</v>
+        <v>5028043.369666</v>
       </c>
       <c r="P6" t="n">
-        <v>5508357.882845</v>
+        <v>5510107.488194</v>
       </c>
       <c r="Q6" t="n">
-        <v>5953909.197031</v>
+        <v>5955732.779958</v>
       </c>
       <c r="R6" t="n">
-        <v>6336374.866106</v>
+        <v>6338197.397147</v>
       </c>
       <c r="S6" t="n">
-        <v>6596168.026089</v>
+        <v>6598001.765654</v>
       </c>
       <c r="T6" t="n">
-        <v>6706884.899854</v>
+        <v>6708854.485767</v>
       </c>
       <c r="U6" t="n">
-        <v>6664569.833279</v>
+        <v>6666940.185946</v>
       </c>
       <c r="V6" t="n">
-        <v>6509788.763314</v>
+        <v>6512892.233687</v>
       </c>
     </row>
     <row r="7">
@@ -906,58 +906,58 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>644945.1078999999</v>
+        <v>644949.380057</v>
       </c>
       <c r="F7" t="n">
-        <v>672912.530522</v>
+        <v>672913.2652</v>
       </c>
       <c r="G7" t="n">
-        <v>840177.906261</v>
+        <v>840145.826216</v>
       </c>
       <c r="H7" t="n">
-        <v>1120833.239676</v>
+        <v>1120727.427595</v>
       </c>
       <c r="I7" t="n">
-        <v>1539143.045075</v>
+        <v>1538912.567263</v>
       </c>
       <c r="J7" t="n">
-        <v>2145851.231436</v>
+        <v>2145432.753948</v>
       </c>
       <c r="K7" t="n">
-        <v>2794775.333426</v>
+        <v>2794143.248148</v>
       </c>
       <c r="L7" t="n">
-        <v>3440642.945228</v>
+        <v>3439820.448349</v>
       </c>
       <c r="M7" t="n">
-        <v>4022462.638589</v>
+        <v>4021519.307119</v>
       </c>
       <c r="N7" t="n">
-        <v>4485528.148582</v>
+        <v>4484571.274776</v>
       </c>
       <c r="O7" t="n">
-        <v>4739114.239242</v>
+        <v>4738287.198845</v>
       </c>
       <c r="P7" t="n">
-        <v>4814313.990357</v>
+        <v>4813743.118346</v>
       </c>
       <c r="Q7" t="n">
-        <v>4734884.722687</v>
+        <v>4734681.910528</v>
       </c>
       <c r="R7" t="n">
-        <v>4565809.211072</v>
+        <v>4566045.261087</v>
       </c>
       <c r="S7" t="n">
-        <v>4351087.190163</v>
+        <v>4351815.036651</v>
       </c>
       <c r="T7" t="n">
-        <v>4136207.016569</v>
+        <v>4137477.548211</v>
       </c>
       <c r="U7" t="n">
-        <v>3919942.309435</v>
+        <v>3921886.873926</v>
       </c>
       <c r="V7" t="n">
-        <v>3708499.476319</v>
+        <v>3711323.340776</v>
       </c>
     </row>
     <row r="8">
@@ -982,58 +982,58 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>189893.211304</v>
+        <v>189919.487563</v>
       </c>
       <c r="F8" t="n">
-        <v>190203.932326</v>
+        <v>190253.487869</v>
       </c>
       <c r="G8" t="n">
-        <v>218385.402386</v>
+        <v>218464.133734</v>
       </c>
       <c r="H8" t="n">
-        <v>263101.506705</v>
+        <v>263222.41156</v>
       </c>
       <c r="I8" t="n">
-        <v>331625.254586</v>
+        <v>331809.882484</v>
       </c>
       <c r="J8" t="n">
-        <v>434072.098857</v>
+        <v>434355.332756</v>
       </c>
       <c r="K8" t="n">
-        <v>545731.9672599999</v>
+        <v>546137.446414</v>
       </c>
       <c r="L8" t="n">
-        <v>669256.585724</v>
+        <v>669808.425836</v>
       </c>
       <c r="M8" t="n">
-        <v>798508.045756</v>
+        <v>799228.524918</v>
       </c>
       <c r="N8" t="n">
-        <v>925224.421895</v>
+        <v>926131.195833</v>
       </c>
       <c r="O8" t="n">
-        <v>1028451.125855</v>
+        <v>1029544.318416</v>
       </c>
       <c r="P8" t="n">
-        <v>1109293.008109</v>
+        <v>1110571.793692</v>
       </c>
       <c r="Q8" t="n">
-        <v>1163309.640364</v>
+        <v>1164774.759877</v>
       </c>
       <c r="R8" t="n">
-        <v>1199254.496198</v>
+        <v>1200914.427653</v>
       </c>
       <c r="S8" t="n">
-        <v>1218415.639543</v>
+        <v>1220293.54644</v>
       </c>
       <c r="T8" t="n">
-        <v>1225027.583458</v>
+        <v>1227174.258228</v>
       </c>
       <c r="U8" t="n">
-        <v>1215036.751846</v>
+        <v>1217548.245992</v>
       </c>
       <c r="V8" t="n">
-        <v>1189945.118257</v>
+        <v>1192982.629057</v>
       </c>
     </row>
     <row r="9">
@@ -1058,58 +1058,58 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8194.019849</v>
+        <v>8205.544766000001</v>
       </c>
       <c r="F9" t="n">
-        <v>6388.642443</v>
+        <v>6407.16054</v>
       </c>
       <c r="G9" t="n">
-        <v>5631.008189</v>
+        <v>5656.525197</v>
       </c>
       <c r="H9" t="n">
-        <v>5499.762356</v>
+        <v>5533.926896</v>
       </c>
       <c r="I9" t="n">
-        <v>5878.742627</v>
+        <v>5924.862774</v>
       </c>
       <c r="J9" t="n">
-        <v>6800.875264</v>
+        <v>6864.452025</v>
       </c>
       <c r="K9" t="n">
-        <v>7717.408137</v>
+        <v>7800.419323</v>
       </c>
       <c r="L9" t="n">
-        <v>8676.048253999999</v>
+        <v>8780.640617999999</v>
       </c>
       <c r="M9" t="n">
-        <v>9537.378102999999</v>
+        <v>9664.720013</v>
       </c>
       <c r="N9" t="n">
-        <v>10161.280114</v>
+        <v>10311.182918</v>
       </c>
       <c r="O9" t="n">
-        <v>10328.790532</v>
+        <v>10497.660153</v>
       </c>
       <c r="P9" t="n">
-        <v>10382.737272</v>
+        <v>10569.19192</v>
       </c>
       <c r="Q9" t="n">
-        <v>10268.622408</v>
+        <v>10471.097598</v>
       </c>
       <c r="R9" t="n">
-        <v>10059.761738</v>
+        <v>10278.551109</v>
       </c>
       <c r="S9" t="n">
-        <v>9766.779757</v>
+        <v>10003.630185</v>
       </c>
       <c r="T9" t="n">
-        <v>9502.410329</v>
+        <v>9762.116841999999</v>
       </c>
       <c r="U9" t="n">
-        <v>9273.492302000001</v>
+        <v>9563.469327000001</v>
       </c>
       <c r="V9" t="n">
-        <v>9151.155768000001</v>
+        <v>9484.930130999999</v>
       </c>
     </row>
     <row r="10">
@@ -1134,58 +1134,58 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>120537.014659</v>
+        <v>120551.729642</v>
       </c>
       <c r="F10" t="n">
-        <v>112938.666142</v>
+        <v>112968.243743</v>
       </c>
       <c r="G10" t="n">
-        <v>115874.192136</v>
+        <v>115924.806642</v>
       </c>
       <c r="H10" t="n">
-        <v>129238.375496</v>
+        <v>129318.932553</v>
       </c>
       <c r="I10" t="n">
-        <v>155216.112824</v>
+        <v>155341.687659</v>
       </c>
       <c r="J10" t="n">
-        <v>199344.936411</v>
+        <v>199539.804343</v>
       </c>
       <c r="K10" t="n">
-        <v>251741.581352</v>
+        <v>252022.133641</v>
       </c>
       <c r="L10" t="n">
-        <v>315116.567577</v>
+        <v>315499.119752</v>
       </c>
       <c r="M10" t="n">
-        <v>387110.910214</v>
+        <v>387609.702626</v>
       </c>
       <c r="N10" t="n">
-        <v>465050.629962</v>
+        <v>465676.385482</v>
       </c>
       <c r="O10" t="n">
-        <v>535231.010148</v>
+        <v>535984.3176750001</v>
       </c>
       <c r="P10" t="n">
-        <v>592976.593993</v>
+        <v>593859.97247</v>
       </c>
       <c r="Q10" t="n">
-        <v>631217.6336459999</v>
+        <v>632236.422577</v>
       </c>
       <c r="R10" t="n">
-        <v>654726.829382</v>
+        <v>655893.7683840001</v>
       </c>
       <c r="S10" t="n">
-        <v>679076.869622</v>
+        <v>680407.766904</v>
       </c>
       <c r="T10" t="n">
-        <v>705806.604466</v>
+        <v>707337.226959</v>
       </c>
       <c r="U10" t="n">
-        <v>727390.451415</v>
+        <v>729189.612187</v>
       </c>
       <c r="V10" t="n">
-        <v>738291.291243</v>
+        <v>740480.510368</v>
       </c>
     </row>
     <row r="11">
@@ -1210,58 +1210,58 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>384817.752784</v>
+        <v>384985.164625</v>
       </c>
       <c r="F11" t="n">
-        <v>374055.132824</v>
+        <v>374361.74825</v>
       </c>
       <c r="G11" t="n">
-        <v>418957.4976</v>
+        <v>419437.372823</v>
       </c>
       <c r="H11" t="n">
-        <v>501949.206271</v>
+        <v>502668.047216</v>
       </c>
       <c r="I11" t="n">
-        <v>627111.863194</v>
+        <v>628179.721786</v>
       </c>
       <c r="J11" t="n">
-        <v>779719.434873</v>
+        <v>781306.7973109999</v>
       </c>
       <c r="K11" t="n">
-        <v>917409.832119</v>
+        <v>919613.600712</v>
       </c>
       <c r="L11" t="n">
-        <v>1056476.932335</v>
+        <v>1059395.876547</v>
       </c>
       <c r="M11" t="n">
-        <v>1207515.793584</v>
+        <v>1211240.259394</v>
       </c>
       <c r="N11" t="n">
-        <v>1358157.193886</v>
+        <v>1362754.847686</v>
       </c>
       <c r="O11" t="n">
-        <v>1469694.748026</v>
+        <v>1475136.674424</v>
       </c>
       <c r="P11" t="n">
-        <v>1532688.245033</v>
+        <v>1538939.735506</v>
       </c>
       <c r="Q11" t="n">
-        <v>1539381.12817</v>
+        <v>1546395.065543</v>
       </c>
       <c r="R11" t="n">
-        <v>1503861.148412</v>
+        <v>1511641.346756</v>
       </c>
       <c r="S11" t="n">
-        <v>1440588.455912</v>
+        <v>1449200.537801</v>
       </c>
       <c r="T11" t="n">
-        <v>1368695.373735</v>
+        <v>1378329.889676</v>
       </c>
       <c r="U11" t="n">
-        <v>1293535.608735</v>
+        <v>1304516.753709</v>
       </c>
       <c r="V11" t="n">
-        <v>1226135.963771</v>
+        <v>1239050.303246</v>
       </c>
     </row>
     <row r="12">
@@ -1286,58 +1286,58 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>481799.977165</v>
+        <v>481681.905293</v>
       </c>
       <c r="F12" t="n">
-        <v>487314.970484</v>
+        <v>487095.481648</v>
       </c>
       <c r="G12" t="n">
-        <v>581258.010094</v>
+        <v>580891.625778</v>
       </c>
       <c r="H12" t="n">
-        <v>734045.802807</v>
+        <v>733465.991198</v>
       </c>
       <c r="I12" t="n">
-        <v>954719.806465</v>
+        <v>953831.378807</v>
       </c>
       <c r="J12" t="n">
-        <v>1286225.416313</v>
+        <v>1284867.769836</v>
       </c>
       <c r="K12" t="n">
-        <v>1648388.562337</v>
+        <v>1646461.569083</v>
       </c>
       <c r="L12" t="n">
-        <v>2050558.846662</v>
+        <v>2047944.441596</v>
       </c>
       <c r="M12" t="n">
-        <v>2466574.439961</v>
+        <v>2463171.594253</v>
       </c>
       <c r="N12" t="n">
-        <v>2862777.397856</v>
+        <v>2858519.236198</v>
       </c>
       <c r="O12" t="n">
-        <v>3185595.852179</v>
+        <v>3180487.618643</v>
       </c>
       <c r="P12" t="n">
-        <v>3449743.363094</v>
+        <v>3443759.140695</v>
       </c>
       <c r="Q12" t="n">
-        <v>3645124.472598</v>
+        <v>3638243.098238</v>
       </c>
       <c r="R12" t="n">
-        <v>3781263.02243</v>
+        <v>3773406.629273</v>
       </c>
       <c r="S12" t="n">
-        <v>3862110.009961</v>
+        <v>3853134.724738</v>
       </c>
       <c r="T12" t="n">
-        <v>3908527.605119</v>
+        <v>3898134.432078</v>
       </c>
       <c r="U12" t="n">
-        <v>3913567.228946</v>
+        <v>3901344.743966</v>
       </c>
       <c r="V12" t="n">
-        <v>3882958.635321</v>
+        <v>3868143.835104</v>
       </c>
     </row>
     <row r="13">
@@ -1362,58 +1362,58 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>512624.162591</v>
+        <v>512640.496646</v>
       </c>
       <c r="F13" t="n">
-        <v>514344.799284</v>
+        <v>514381.732752</v>
       </c>
       <c r="G13" t="n">
-        <v>580089.767087</v>
+        <v>580160.602229</v>
       </c>
       <c r="H13" t="n">
-        <v>706035.317772</v>
+        <v>706158.407459</v>
       </c>
       <c r="I13" t="n">
-        <v>917444.129152</v>
+        <v>917647.6019379999</v>
       </c>
       <c r="J13" t="n">
-        <v>1254230.52197</v>
+        <v>1254558.922776</v>
       </c>
       <c r="K13" t="n">
-        <v>1654175.914466</v>
+        <v>1654661.37171</v>
       </c>
       <c r="L13" t="n">
-        <v>2118013.715242</v>
+        <v>2118693.409047</v>
       </c>
       <c r="M13" t="n">
-        <v>2612484.428025</v>
+        <v>2613407.322241</v>
       </c>
       <c r="N13" t="n">
-        <v>3087236.385752</v>
+        <v>3088467.920684</v>
       </c>
       <c r="O13" t="n">
-        <v>3453080.219165</v>
+        <v>3454684.751517</v>
       </c>
       <c r="P13" t="n">
-        <v>3699598.569301</v>
+        <v>3701649.629708</v>
       </c>
       <c r="Q13" t="n">
-        <v>3820285.067147</v>
+        <v>3822863.26851</v>
       </c>
       <c r="R13" t="n">
-        <v>3857299.699778</v>
+        <v>3860487.559072</v>
       </c>
       <c r="S13" t="n">
-        <v>3877199.94353</v>
+        <v>3881060.536524</v>
       </c>
       <c r="T13" t="n">
-        <v>3900975.040592</v>
+        <v>3905630.70055</v>
       </c>
       <c r="U13" t="n">
-        <v>3905473.587977</v>
+        <v>3911186.182199</v>
       </c>
       <c r="V13" t="n">
-        <v>3878516.894864</v>
+        <v>3885743.794884</v>
       </c>
     </row>
     <row r="14">
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1102.335005</v>
+        <v>1100.830636</v>
       </c>
       <c r="F14" t="n">
-        <v>1268.053717</v>
+        <v>1263.643014</v>
       </c>
       <c r="G14" t="n">
-        <v>2465.069169</v>
+        <v>2447.384311</v>
       </c>
       <c r="H14" t="n">
-        <v>4444.983742</v>
+        <v>4379.394673</v>
       </c>
       <c r="I14" t="n">
-        <v>8073.01014</v>
+        <v>7784.030005</v>
       </c>
       <c r="J14" t="n">
         <v>764488.204664</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>203615.083804</v>
+        <v>203616.01612</v>
       </c>
       <c r="F15" t="n">
-        <v>254959.068926</v>
+        <v>254961.470843</v>
       </c>
       <c r="G15" t="n">
-        <v>509885.217341</v>
+        <v>509893.887385</v>
       </c>
       <c r="H15" t="n">
-        <v>908400.8234699999</v>
+        <v>908431.4269589999</v>
       </c>
       <c r="I15" t="n">
-        <v>1511688.507056</v>
+        <v>1511821.580031</v>
       </c>
       <c r="J15" t="n">
         <v>1884649.090138</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>25204.635768</v>
+        <v>25203.931279</v>
       </c>
       <c r="F16" t="n">
-        <v>24706.057562</v>
+        <v>24704.437933</v>
       </c>
       <c r="G16" t="n">
-        <v>39237.196072</v>
+        <v>39232.419822</v>
       </c>
       <c r="H16" t="n">
-        <v>59068.534949</v>
+        <v>59054.782159</v>
       </c>
       <c r="I16" t="n">
-        <v>88290.670128</v>
+        <v>88240.090709</v>
       </c>
       <c r="J16" t="n">
         <v>239582.825334</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73239.440522</v>
+        <v>73240.245301</v>
       </c>
       <c r="F17" t="n">
-        <v>85563.43185199999</v>
+        <v>85565.71716</v>
       </c>
       <c r="G17" t="n">
-        <v>161925.850545</v>
+        <v>161934.601645</v>
       </c>
       <c r="H17" t="n">
-        <v>274582.034975</v>
+        <v>274613.121368</v>
       </c>
       <c r="I17" t="n">
-        <v>438821.566724</v>
+        <v>438953.417067</v>
       </c>
       <c r="J17" t="n">
         <v>294879.946041</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>51162.746301</v>
+        <v>51163.218064</v>
       </c>
       <c r="F18" t="n">
-        <v>61296.21876</v>
+        <v>61297.561868</v>
       </c>
       <c r="G18" t="n">
-        <v>112316.697427</v>
+        <v>112321.737391</v>
       </c>
       <c r="H18" t="n">
-        <v>184470.387749</v>
+        <v>184488.039725</v>
       </c>
       <c r="I18" t="n">
-        <v>290777.963632</v>
+        <v>290852.599868</v>
       </c>
       <c r="J18" t="n">
         <v>231848.299883</v>
@@ -1818,58 +1818,58 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223984.580786</v>
+        <v>224089.657199</v>
       </c>
       <c r="F19" t="n">
-        <v>233606.455012</v>
+        <v>233812.622971</v>
       </c>
       <c r="G19" t="n">
-        <v>247268.484006</v>
+        <v>247583.706904</v>
       </c>
       <c r="H19" t="n">
-        <v>266583.578327</v>
+        <v>267025.055523</v>
       </c>
       <c r="I19" t="n">
-        <v>307020.732886</v>
+        <v>307642.133715</v>
       </c>
       <c r="J19" t="n">
-        <v>375439.789851</v>
+        <v>376332.688105</v>
       </c>
       <c r="K19" t="n">
-        <v>449878.311495</v>
+        <v>451100.961289</v>
       </c>
       <c r="L19" t="n">
-        <v>530236.05947</v>
+        <v>531850.508704</v>
       </c>
       <c r="M19" t="n">
-        <v>614096.214284</v>
+        <v>616166.3593670001</v>
       </c>
       <c r="N19" t="n">
-        <v>698007.064076</v>
+        <v>700598.5457970001</v>
       </c>
       <c r="O19" t="n">
-        <v>773519.834389</v>
+        <v>776683.424671</v>
       </c>
       <c r="P19" t="n">
-        <v>830952.285384</v>
+        <v>834710.068236</v>
       </c>
       <c r="Q19" t="n">
-        <v>872381.622511</v>
+        <v>876775.842951</v>
       </c>
       <c r="R19" t="n">
-        <v>902234.939133</v>
+        <v>907345.420648</v>
       </c>
       <c r="S19" t="n">
-        <v>923502.094573</v>
+        <v>929461.154769</v>
       </c>
       <c r="T19" t="n">
-        <v>932190.7666560001</v>
+        <v>939167.942039</v>
       </c>
       <c r="U19" t="n">
-        <v>930874.362182</v>
+        <v>939161.741388</v>
       </c>
       <c r="V19" t="n">
-        <v>922183.644502</v>
+        <v>932304.5310439999</v>
       </c>
     </row>
     <row r="20">
@@ -1894,58 +1894,58 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>21279.866513</v>
+        <v>21296.108529</v>
       </c>
       <c r="F20" t="n">
-        <v>20302.138416</v>
+        <v>20331.577268</v>
       </c>
       <c r="G20" t="n">
-        <v>21319.567065</v>
+        <v>21361.894109</v>
       </c>
       <c r="H20" t="n">
-        <v>22737.026078</v>
+        <v>22792.968128</v>
       </c>
       <c r="I20" t="n">
-        <v>25219.238282</v>
+        <v>25293.57789</v>
       </c>
       <c r="J20" t="n">
-        <v>28756.135321</v>
+        <v>28856.92131</v>
       </c>
       <c r="K20" t="n">
-        <v>31321.425477</v>
+        <v>31451.514054</v>
       </c>
       <c r="L20" t="n">
-        <v>32938.218238</v>
+        <v>33099.897466</v>
       </c>
       <c r="M20" t="n">
-        <v>33847.260422</v>
+        <v>34042.22943</v>
       </c>
       <c r="N20" t="n">
-        <v>34221.932361</v>
+        <v>34451.654236</v>
       </c>
       <c r="O20" t="n">
-        <v>33947.807169</v>
+        <v>34211.769258</v>
       </c>
       <c r="P20" t="n">
-        <v>32885.131451</v>
+        <v>33180.670454</v>
       </c>
       <c r="Q20" t="n">
-        <v>31408.50964</v>
+        <v>31735.108491</v>
       </c>
       <c r="R20" t="n">
-        <v>29807.182</v>
+        <v>30167.183628</v>
       </c>
       <c r="S20" t="n">
-        <v>28253.268242</v>
+        <v>28652.500891</v>
       </c>
       <c r="T20" t="n">
-        <v>26687.727264</v>
+        <v>27134.007759</v>
       </c>
       <c r="U20" t="n">
-        <v>25234.228082</v>
+        <v>25742.314026</v>
       </c>
       <c r="V20" t="n">
-        <v>23987.042273</v>
+        <v>24583.823114</v>
       </c>
     </row>
     <row r="21">
@@ -1970,58 +1970,58 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100121.935658</v>
+        <v>100099.079401</v>
       </c>
       <c r="F21" t="n">
-        <v>83922.431964</v>
+        <v>83888.40384699999</v>
       </c>
       <c r="G21" t="n">
-        <v>77754.901904</v>
+        <v>77712.479005</v>
       </c>
       <c r="H21" t="n">
-        <v>79019.227631</v>
+        <v>78967.36972800001</v>
       </c>
       <c r="I21" t="n">
-        <v>89253.964565</v>
+        <v>89187.424658</v>
       </c>
       <c r="J21" t="n">
-        <v>108643.102819</v>
+        <v>108554.196837</v>
       </c>
       <c r="K21" t="n">
-        <v>129439.948903</v>
+        <v>129326.18206</v>
       </c>
       <c r="L21" t="n">
-        <v>150626.2595</v>
+        <v>150486.27007</v>
       </c>
       <c r="M21" t="n">
-        <v>171383.23797</v>
+        <v>171216.091004</v>
       </c>
       <c r="N21" t="n">
-        <v>190944.405657</v>
+        <v>190749.655335</v>
       </c>
       <c r="O21" t="n">
-        <v>211029.52566</v>
+        <v>210802.740274</v>
       </c>
       <c r="P21" t="n">
-        <v>227723.643954</v>
+        <v>227463.847439</v>
       </c>
       <c r="Q21" t="n">
-        <v>239049.780425</v>
+        <v>238757.709008</v>
       </c>
       <c r="R21" t="n">
-        <v>243408.053859</v>
+        <v>243086.206026</v>
       </c>
       <c r="S21" t="n">
-        <v>241777.75231</v>
+        <v>241426.325511</v>
       </c>
       <c r="T21" t="n">
-        <v>234674.655956</v>
+        <v>234291.44897</v>
       </c>
       <c r="U21" t="n">
-        <v>224419.998488</v>
+        <v>223995.764874</v>
       </c>
       <c r="V21" t="n">
-        <v>212511.993789</v>
+        <v>212026.874444</v>
       </c>
     </row>
     <row r="22">
@@ -2046,58 +2046,58 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>247427.444868</v>
+        <v>247449.373754</v>
       </c>
       <c r="F22" t="n">
-        <v>259742.57148</v>
+        <v>259782.202128</v>
       </c>
       <c r="G22" t="n">
-        <v>276909.826354</v>
+        <v>276969.434227</v>
       </c>
       <c r="H22" t="n">
-        <v>298567.50541</v>
+        <v>298654.772645</v>
       </c>
       <c r="I22" t="n">
-        <v>343461.188806</v>
+        <v>343591.09356</v>
       </c>
       <c r="J22" t="n">
-        <v>414306.530874</v>
+        <v>414505.222628</v>
       </c>
       <c r="K22" t="n">
-        <v>489292.952644</v>
+        <v>489578.310633</v>
       </c>
       <c r="L22" t="n">
-        <v>572762.770117</v>
+        <v>573151.710082</v>
       </c>
       <c r="M22" t="n">
-        <v>669498.496237</v>
+        <v>670004.725222</v>
       </c>
       <c r="N22" t="n">
-        <v>777964.537033</v>
+        <v>778602.081293</v>
       </c>
       <c r="O22" t="n">
-        <v>888171.537774</v>
+        <v>888952.346032</v>
       </c>
       <c r="P22" t="n">
-        <v>984943.5129110001</v>
+        <v>985874.101169</v>
       </c>
       <c r="Q22" t="n">
-        <v>1066075.042554</v>
+        <v>1067167.270381</v>
       </c>
       <c r="R22" t="n">
-        <v>1131259.810628</v>
+        <v>1132534.31785</v>
       </c>
       <c r="S22" t="n">
-        <v>1179692.427995</v>
+        <v>1181182.582202</v>
       </c>
       <c r="T22" t="n">
-        <v>1203839.516111</v>
+        <v>1205589.171057</v>
       </c>
       <c r="U22" t="n">
-        <v>1205859.917679</v>
+        <v>1207945.991868</v>
       </c>
       <c r="V22" t="n">
-        <v>1188951.574263</v>
+        <v>1191512.518827</v>
       </c>
     </row>
     <row r="23">
@@ -2122,58 +2122,58 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>758990.188182</v>
+        <v>758799.685545</v>
       </c>
       <c r="F23" t="n">
-        <v>823226.066915</v>
+        <v>822842.557796</v>
       </c>
       <c r="G23" t="n">
-        <v>933745.389097</v>
+        <v>933140.250376</v>
       </c>
       <c r="H23" t="n">
-        <v>1097248.115338</v>
+        <v>1096376.218371</v>
       </c>
       <c r="I23" t="n">
-        <v>1374354.483</v>
+        <v>1373103.535799</v>
       </c>
       <c r="J23" t="n">
-        <v>1816110.790716</v>
+        <v>1814289.09542</v>
       </c>
       <c r="K23" t="n">
-        <v>2328966.161752</v>
+        <v>2326447.425077</v>
       </c>
       <c r="L23" t="n">
-        <v>2917066.929423</v>
+        <v>2913710.316226</v>
       </c>
       <c r="M23" t="n">
-        <v>3571609.73962</v>
+        <v>3567264.25148</v>
       </c>
       <c r="N23" t="n">
-        <v>4285925.436927</v>
+        <v>4280423.215776</v>
       </c>
       <c r="O23" t="n">
-        <v>5013991.565699</v>
+        <v>5007188.697522</v>
       </c>
       <c r="P23" t="n">
-        <v>5680537.991345</v>
+        <v>5672348.920365</v>
       </c>
       <c r="Q23" t="n">
-        <v>6269229.337453</v>
+        <v>6259527.583107</v>
       </c>
       <c r="R23" t="n">
-        <v>6773542.798335</v>
+        <v>6762120.724251</v>
       </c>
       <c r="S23" t="n">
-        <v>7189572.025864</v>
+        <v>7176102.740263</v>
       </c>
       <c r="T23" t="n">
-        <v>7474461.11493</v>
+        <v>7458526.86739</v>
       </c>
       <c r="U23" t="n">
-        <v>7639329.395639</v>
+        <v>7620223.114392</v>
       </c>
       <c r="V23" t="n">
-        <v>7692725.237337</v>
+        <v>7669191.652172</v>
       </c>
     </row>
     <row r="24">
@@ -2198,58 +2198,58 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>11435.111608</v>
+        <v>11451.82103</v>
       </c>
       <c r="F24" t="n">
-        <v>11024.268738</v>
+        <v>11054.804028</v>
       </c>
       <c r="G24" t="n">
-        <v>11366.770392</v>
+        <v>11410.87783</v>
       </c>
       <c r="H24" t="n">
-        <v>12067.312451</v>
+        <v>12125.882646</v>
       </c>
       <c r="I24" t="n">
-        <v>13534.825495</v>
+        <v>13612.90418</v>
       </c>
       <c r="J24" t="n">
-        <v>15891.289904</v>
+        <v>15997.431253</v>
       </c>
       <c r="K24" t="n">
-        <v>17983.213614</v>
+        <v>18120.488201</v>
       </c>
       <c r="L24" t="n">
-        <v>19688.136429</v>
+        <v>19859.014782</v>
       </c>
       <c r="M24" t="n">
-        <v>20928.664749</v>
+        <v>21134.873288</v>
       </c>
       <c r="N24" t="n">
-        <v>21662.768524</v>
+        <v>21905.370107</v>
       </c>
       <c r="O24" t="n">
-        <v>21792.588885</v>
+        <v>22070.769096</v>
       </c>
       <c r="P24" t="n">
-        <v>21262.445411</v>
+        <v>21572.926557</v>
       </c>
       <c r="Q24" t="n">
-        <v>20357.637438</v>
+        <v>20699.281328</v>
       </c>
       <c r="R24" t="n">
-        <v>19333.685202</v>
+        <v>19708.576485</v>
       </c>
       <c r="S24" t="n">
-        <v>18430.991614</v>
+        <v>18845.699564</v>
       </c>
       <c r="T24" t="n">
-        <v>17655.334836</v>
+        <v>18119.2223</v>
       </c>
       <c r="U24" t="n">
-        <v>17074.998269</v>
+        <v>17605.116</v>
       </c>
       <c r="V24" t="n">
-        <v>16729.973235</v>
+        <v>17356.584375</v>
       </c>
     </row>
     <row r="25">
@@ -2274,58 +2274,58 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>23649.212351</v>
+        <v>23650.242715</v>
       </c>
       <c r="F25" t="n">
-        <v>21074.952327</v>
+        <v>21077.542967</v>
       </c>
       <c r="G25" t="n">
-        <v>20932.627756</v>
+        <v>20936.715007</v>
       </c>
       <c r="H25" t="n">
-        <v>22396.702804</v>
+        <v>22402.28234</v>
       </c>
       <c r="I25" t="n">
-        <v>25579.197315</v>
+        <v>25587.076284</v>
       </c>
       <c r="J25" t="n">
-        <v>30516.481495</v>
+        <v>30528.260912</v>
       </c>
       <c r="K25" t="n">
-        <v>34988.982176</v>
+        <v>35006.075499</v>
       </c>
       <c r="L25" t="n">
-        <v>38835.384</v>
+        <v>38859.35511</v>
       </c>
       <c r="M25" t="n">
-        <v>41873.731674</v>
+        <v>41906.100607</v>
       </c>
       <c r="N25" t="n">
-        <v>43958.199877</v>
+        <v>44000.406379</v>
       </c>
       <c r="O25" t="n">
-        <v>44779.354405</v>
+        <v>44832.408064</v>
       </c>
       <c r="P25" t="n">
-        <v>44107.169242</v>
+        <v>44171.341128</v>
       </c>
       <c r="Q25" t="n">
-        <v>42484.56993</v>
+        <v>42560.244628</v>
       </c>
       <c r="R25" t="n">
-        <v>40399.240811</v>
+        <v>40487.245258</v>
       </c>
       <c r="S25" t="n">
-        <v>38178.293137</v>
+        <v>38280.272029</v>
       </c>
       <c r="T25" t="n">
-        <v>35807.98795</v>
+        <v>35926.240828</v>
       </c>
       <c r="U25" t="n">
-        <v>33614.550144</v>
+        <v>33753.476025</v>
       </c>
       <c r="V25" t="n">
-        <v>31863.151018</v>
+        <v>32031.017037</v>
       </c>
     </row>
     <row r="26">
@@ -2350,58 +2350,58 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>528456.0437940001</v>
+        <v>528526.903871</v>
       </c>
       <c r="F26" t="n">
-        <v>539710.111272</v>
+        <v>539850.431401</v>
       </c>
       <c r="G26" t="n">
-        <v>542585.619218</v>
+        <v>542813.6702779999</v>
       </c>
       <c r="H26" t="n">
-        <v>550824.268368</v>
+        <v>551167.031786</v>
       </c>
       <c r="I26" t="n">
-        <v>603082.176314</v>
+        <v>603591.651705</v>
       </c>
       <c r="J26" t="n">
-        <v>713085.2325489999</v>
+        <v>713844.4112720001</v>
       </c>
       <c r="K26" t="n">
-        <v>839354.347584</v>
+        <v>840417.798219</v>
       </c>
       <c r="L26" t="n">
-        <v>983693.686222</v>
+        <v>985119.119986</v>
       </c>
       <c r="M26" t="n">
-        <v>1137470.394386</v>
+        <v>1139319.204379</v>
       </c>
       <c r="N26" t="n">
-        <v>1290709.135558</v>
+        <v>1293047.129041</v>
       </c>
       <c r="O26" t="n">
-        <v>1426585.390114</v>
+        <v>1429469.515835</v>
       </c>
       <c r="P26" t="n">
-        <v>1526385.332024</v>
+        <v>1529847.578203</v>
       </c>
       <c r="Q26" t="n">
-        <v>1594227.030005</v>
+        <v>1598317.706437</v>
       </c>
       <c r="R26" t="n">
-        <v>1643999.895988</v>
+        <v>1648803.686334</v>
       </c>
       <c r="S26" t="n">
-        <v>1683296.054445</v>
+        <v>1688949.229761</v>
       </c>
       <c r="T26" t="n">
-        <v>1702860.167759</v>
+        <v>1709538.897529</v>
       </c>
       <c r="U26" t="n">
-        <v>1703900.443226</v>
+        <v>1711903.697496</v>
       </c>
       <c r="V26" t="n">
-        <v>1686718.17738</v>
+        <v>1696574.82108</v>
       </c>
     </row>
     <row r="27">
@@ -2426,58 +2426,58 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>287353.267027</v>
+        <v>287345.370467</v>
       </c>
       <c r="F27" t="n">
-        <v>295566.963152</v>
+        <v>295553.650843</v>
       </c>
       <c r="G27" t="n">
-        <v>306453.800407</v>
+        <v>306442.429173</v>
       </c>
       <c r="H27" t="n">
-        <v>330075.372272</v>
+        <v>330072.370601</v>
       </c>
       <c r="I27" t="n">
-        <v>383254.393961</v>
+        <v>383267.466337</v>
       </c>
       <c r="J27" t="n">
-        <v>474952.00341</v>
+        <v>474992.28661</v>
       </c>
       <c r="K27" t="n">
-        <v>573942.339015</v>
+        <v>574023.984975</v>
       </c>
       <c r="L27" t="n">
-        <v>676280.089097</v>
+        <v>676421.388443</v>
       </c>
       <c r="M27" t="n">
-        <v>775120.073843</v>
+        <v>775344.547239</v>
       </c>
       <c r="N27" t="n">
-        <v>863973.052194</v>
+        <v>864309.827538</v>
       </c>
       <c r="O27" t="n">
-        <v>932582.877162</v>
+        <v>933063.080401</v>
       </c>
       <c r="P27" t="n">
-        <v>972134.700132</v>
+        <v>972783.328267</v>
       </c>
       <c r="Q27" t="n">
-        <v>989687.159338</v>
+        <v>990528.065007</v>
       </c>
       <c r="R27" t="n">
-        <v>992944.4215920001</v>
+        <v>994005.410532</v>
       </c>
       <c r="S27" t="n">
-        <v>987641.574405</v>
+        <v>988961.205149</v>
       </c>
       <c r="T27" t="n">
-        <v>971867.91007</v>
+        <v>973495.757019</v>
       </c>
       <c r="U27" t="n">
-        <v>949539.0527229999</v>
+        <v>951558.723181</v>
       </c>
       <c r="V27" t="n">
-        <v>922800.169185</v>
+        <v>925361.220966</v>
       </c>
     </row>
     <row r="28">
@@ -2502,58 +2502,58 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>95764.027413</v>
+        <v>95753.43568900001</v>
       </c>
       <c r="F28" t="n">
-        <v>89463.766754</v>
+        <v>89445.932781</v>
       </c>
       <c r="G28" t="n">
-        <v>105524.962119</v>
+        <v>105490.49141</v>
       </c>
       <c r="H28" t="n">
-        <v>137138.140859</v>
+        <v>137073.297771</v>
       </c>
       <c r="I28" t="n">
-        <v>190512.619978</v>
+        <v>190395.956472</v>
       </c>
       <c r="J28" t="n">
-        <v>271809.954029</v>
+        <v>271610.796621</v>
       </c>
       <c r="K28" t="n">
-        <v>365428.891219</v>
+        <v>365123.833869</v>
       </c>
       <c r="L28" t="n">
-        <v>466718.395451</v>
+        <v>466288.347078</v>
       </c>
       <c r="M28" t="n">
-        <v>571044.8676690001</v>
+        <v>570474.2988390001</v>
       </c>
       <c r="N28" t="n">
-        <v>672826.002812</v>
+        <v>672104.649517</v>
       </c>
       <c r="O28" t="n">
-        <v>763760.36424</v>
+        <v>762886.094345</v>
       </c>
       <c r="P28" t="n">
-        <v>834149.576995</v>
+        <v>833129.007032</v>
       </c>
       <c r="Q28" t="n">
-        <v>886092.690406</v>
+        <v>884924.568362</v>
       </c>
       <c r="R28" t="n">
-        <v>922555.922914</v>
+        <v>921227.179446</v>
       </c>
       <c r="S28" t="n">
-        <v>946161.740016</v>
+        <v>944644.512462</v>
       </c>
       <c r="T28" t="n">
-        <v>954122.308968</v>
+        <v>952377.935609</v>
       </c>
       <c r="U28" t="n">
-        <v>950608.673168</v>
+        <v>948565.68035</v>
       </c>
       <c r="V28" t="n">
-        <v>938369.2434189999</v>
+        <v>935897.163341</v>
       </c>
     </row>
     <row r="29">
@@ -2578,58 +2578,58 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>142080.521725</v>
+        <v>142089.506901</v>
       </c>
       <c r="F29" t="n">
-        <v>121014.797088</v>
+        <v>121041.978784</v>
       </c>
       <c r="G29" t="n">
-        <v>113842.759992</v>
+        <v>113895.077883</v>
       </c>
       <c r="H29" t="n">
-        <v>115731.834042</v>
+        <v>115812.882168</v>
       </c>
       <c r="I29" t="n">
-        <v>129736.481459</v>
+        <v>129852.232235</v>
       </c>
       <c r="J29" t="n">
-        <v>153141.256346</v>
+        <v>153297.152844</v>
       </c>
       <c r="K29" t="n">
-        <v>178787.770446</v>
+        <v>178981.327815</v>
       </c>
       <c r="L29" t="n">
-        <v>208898.398632</v>
+        <v>209128.965149</v>
       </c>
       <c r="M29" t="n">
-        <v>244976.939965</v>
+        <v>245247.427271</v>
       </c>
       <c r="N29" t="n">
-        <v>287588.110146</v>
+        <v>287903.666396</v>
       </c>
       <c r="O29" t="n">
-        <v>332074.094065</v>
+        <v>332435.484531</v>
       </c>
       <c r="P29" t="n">
-        <v>375196.237412</v>
+        <v>375601.03658</v>
       </c>
       <c r="Q29" t="n">
-        <v>416086.903484</v>
+        <v>416532.716297</v>
       </c>
       <c r="R29" t="n">
-        <v>460106.727992</v>
+        <v>460588.650515</v>
       </c>
       <c r="S29" t="n">
-        <v>503800.268562</v>
+        <v>504311.62792</v>
       </c>
       <c r="T29" t="n">
-        <v>542576.5239800001</v>
+        <v>543110.862449</v>
       </c>
       <c r="U29" t="n">
-        <v>571556.0540229999</v>
+        <v>572108.980901</v>
       </c>
       <c r="V29" t="n">
-        <v>592853.506142</v>
+        <v>593424.8159620001</v>
       </c>
     </row>
     <row r="30">
@@ -2654,58 +2654,58 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>236754.818423</v>
+        <v>236771.016372</v>
       </c>
       <c r="F30" t="n">
-        <v>190651.597632</v>
+        <v>190702.703898</v>
       </c>
       <c r="G30" t="n">
-        <v>169176.549357</v>
+        <v>169273.370331</v>
       </c>
       <c r="H30" t="n">
-        <v>166927.410322</v>
+        <v>167073.276157</v>
       </c>
       <c r="I30" t="n">
-        <v>181922.51807</v>
+        <v>182128.336178</v>
       </c>
       <c r="J30" t="n">
-        <v>211639.439</v>
+        <v>211915.591687</v>
       </c>
       <c r="K30" t="n">
-        <v>245227.3924</v>
+        <v>245571.254248</v>
       </c>
       <c r="L30" t="n">
-        <v>283420.210259</v>
+        <v>283832.691718</v>
       </c>
       <c r="M30" t="n">
-        <v>333114.910007</v>
+        <v>333602.40988</v>
       </c>
       <c r="N30" t="n">
-        <v>400611.598077</v>
+        <v>401183.045288</v>
       </c>
       <c r="O30" t="n">
-        <v>484030.679593</v>
+        <v>484686.099035</v>
       </c>
       <c r="P30" t="n">
-        <v>578934.284604</v>
+        <v>579666.622213</v>
       </c>
       <c r="Q30" t="n">
-        <v>682197.493854</v>
+        <v>682998.986021</v>
       </c>
       <c r="R30" t="n">
-        <v>789193.90601</v>
+        <v>790057.074994</v>
       </c>
       <c r="S30" t="n">
-        <v>891757.253312</v>
+        <v>892673.048583</v>
       </c>
       <c r="T30" t="n">
-        <v>983859.722224</v>
+        <v>984819.099761</v>
       </c>
       <c r="U30" t="n">
-        <v>1062186.037737</v>
+        <v>1063180.979063</v>
       </c>
       <c r="V30" t="n">
-        <v>1131646.416434</v>
+        <v>1132675.409781</v>
       </c>
     </row>
     <row r="31">
@@ -2730,58 +2730,58 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>407828.859978</v>
+        <v>407679.846807</v>
       </c>
       <c r="F31" t="n">
-        <v>365478.557547</v>
+        <v>365260.069068</v>
       </c>
       <c r="G31" t="n">
-        <v>344646.339379</v>
+        <v>344411.53294</v>
       </c>
       <c r="H31" t="n">
-        <v>351221.000783</v>
+        <v>350977.25323</v>
       </c>
       <c r="I31" t="n">
-        <v>394017.183422</v>
+        <v>393742.638446</v>
       </c>
       <c r="J31" t="n">
-        <v>465489.373203</v>
+        <v>465156.999163</v>
       </c>
       <c r="K31" t="n">
-        <v>540967.089547</v>
+        <v>540564.5730410001</v>
       </c>
       <c r="L31" t="n">
-        <v>627612.58472</v>
+        <v>627123.20991</v>
       </c>
       <c r="M31" t="n">
-        <v>731311.160483</v>
+        <v>730714.573508</v>
       </c>
       <c r="N31" t="n">
-        <v>855625.649242</v>
+        <v>854897.7637820001</v>
       </c>
       <c r="O31" t="n">
-        <v>984856.396585</v>
+        <v>983984.69189</v>
       </c>
       <c r="P31" t="n">
-        <v>1106716.862322</v>
+        <v>1105698.5396</v>
       </c>
       <c r="Q31" t="n">
-        <v>1217360.963653</v>
+        <v>1216195.141859</v>
       </c>
       <c r="R31" t="n">
-        <v>1316423.236527</v>
+        <v>1315107.380435</v>
       </c>
       <c r="S31" t="n">
-        <v>1423948.168737</v>
+        <v>1422453.3202</v>
       </c>
       <c r="T31" t="n">
-        <v>1527922.788384</v>
+        <v>1526230.055607</v>
       </c>
       <c r="U31" t="n">
-        <v>1612026.056785</v>
+        <v>1610134.929605</v>
       </c>
       <c r="V31" t="n">
-        <v>1670442.646679</v>
+        <v>1668362.474152</v>
       </c>
     </row>
     <row r="32">
@@ -2806,58 +2806,58 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>365005.843222</v>
+        <v>365004.825844</v>
       </c>
       <c r="F32" t="n">
-        <v>284626.725593</v>
+        <v>284660.036033</v>
       </c>
       <c r="G32" t="n">
-        <v>246375.792695</v>
+        <v>246458.754668</v>
       </c>
       <c r="H32" t="n">
-        <v>239569.465518</v>
+        <v>239701.309193</v>
       </c>
       <c r="I32" t="n">
-        <v>264376.066674</v>
+        <v>264559.760184</v>
       </c>
       <c r="J32" t="n">
-        <v>311979.689476</v>
+        <v>312217.010702</v>
       </c>
       <c r="K32" t="n">
-        <v>364537.209086</v>
+        <v>364817.806379</v>
       </c>
       <c r="L32" t="n">
-        <v>423090.887997</v>
+        <v>423408.686498</v>
       </c>
       <c r="M32" t="n">
-        <v>487736.07205</v>
+        <v>488092.036228</v>
       </c>
       <c r="N32" t="n">
-        <v>561943.77422</v>
+        <v>562341.184126</v>
       </c>
       <c r="O32" t="n">
-        <v>636024.715261</v>
+        <v>636462.6549739999</v>
       </c>
       <c r="P32" t="n">
-        <v>703078.385142</v>
+        <v>703552.9726569999</v>
       </c>
       <c r="Q32" t="n">
-        <v>760395.919446</v>
+        <v>760904.866988</v>
       </c>
       <c r="R32" t="n">
-        <v>806968.385943</v>
+        <v>807510.3003999999</v>
       </c>
       <c r="S32" t="n">
-        <v>839673.7515210001</v>
+        <v>840246.312666</v>
       </c>
       <c r="T32" t="n">
-        <v>858362.111587</v>
+        <v>858962.0986800001</v>
       </c>
       <c r="U32" t="n">
-        <v>864793.666554</v>
+        <v>865417.406155</v>
       </c>
       <c r="V32" t="n">
-        <v>865992.100771</v>
+        <v>866639.406354</v>
       </c>
     </row>
     <row r="33">
@@ -2882,58 +2882,58 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>379370.871801</v>
+        <v>379387.604247</v>
       </c>
       <c r="F33" t="n">
-        <v>320646.513676</v>
+        <v>320701.633642</v>
       </c>
       <c r="G33" t="n">
-        <v>299192.454628</v>
+        <v>299302.449919</v>
       </c>
       <c r="H33" t="n">
-        <v>303467.324623</v>
+        <v>303638.384938</v>
       </c>
       <c r="I33" t="n">
-        <v>337416.599948</v>
+        <v>337658.841324</v>
       </c>
       <c r="J33" t="n">
-        <v>390673.867219</v>
+        <v>390995.319796</v>
       </c>
       <c r="K33" t="n">
-        <v>440875.413023</v>
+        <v>441268.114992</v>
       </c>
       <c r="L33" t="n">
-        <v>492713.878298</v>
+        <v>493175.007356</v>
       </c>
       <c r="M33" t="n">
-        <v>550611.913217</v>
+        <v>551146.680855</v>
       </c>
       <c r="N33" t="n">
-        <v>615656.164732</v>
+        <v>616274.489023</v>
       </c>
       <c r="O33" t="n">
-        <v>687269.066752</v>
+        <v>687969.113056</v>
       </c>
       <c r="P33" t="n">
-        <v>757062.4127240001</v>
+        <v>757836.682409</v>
       </c>
       <c r="Q33" t="n">
-        <v>819265.063585</v>
+        <v>820108.219821</v>
       </c>
       <c r="R33" t="n">
-        <v>866875.3603919999</v>
+        <v>867785.115902</v>
       </c>
       <c r="S33" t="n">
-        <v>895903.007503</v>
+        <v>896875.283129</v>
       </c>
       <c r="T33" t="n">
-        <v>907334.7583859999</v>
+        <v>908363.686134</v>
       </c>
       <c r="U33" t="n">
-        <v>904617.650929</v>
+        <v>905696.5370520001</v>
       </c>
       <c r="V33" t="n">
-        <v>896090.972004</v>
+        <v>897218.914509</v>
       </c>
     </row>
     <row r="34">
@@ -2958,58 +2958,58 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1603932.723297</v>
+        <v>1603598.397083</v>
       </c>
       <c r="F34" t="n">
-        <v>2375398.89755</v>
+        <v>2374402.530746</v>
       </c>
       <c r="G34" t="n">
-        <v>3755560.546417</v>
+        <v>3753502.366293</v>
       </c>
       <c r="H34" t="n">
-        <v>5498882.60283</v>
+        <v>5495565.580813</v>
       </c>
       <c r="I34" t="n">
-        <v>7665018.567366</v>
+        <v>7660172.93625</v>
       </c>
       <c r="J34" t="n">
-        <v>10036591.323066</v>
+        <v>10029973.202187</v>
       </c>
       <c r="K34" t="n">
-        <v>12045157.33536</v>
+        <v>12036866.749731</v>
       </c>
       <c r="L34" t="n">
-        <v>13857510.7583</v>
+        <v>13847584.54541</v>
       </c>
       <c r="M34" t="n">
-        <v>15726687.653983</v>
+        <v>15715025.999328</v>
       </c>
       <c r="N34" t="n">
-        <v>17770387.21083</v>
+        <v>17756810.390999</v>
       </c>
       <c r="O34" t="n">
-        <v>19717948.430217</v>
+        <v>19702463.064526</v>
       </c>
       <c r="P34" t="n">
-        <v>21396387.321187</v>
+        <v>21379119.43927</v>
       </c>
       <c r="Q34" t="n">
-        <v>22807363.606547</v>
+        <v>22788408.677089</v>
       </c>
       <c r="R34" t="n">
-        <v>23956479.634344</v>
+        <v>23935903.287545</v>
       </c>
       <c r="S34" t="n">
-        <v>24772767.35855</v>
+        <v>24750692.2866</v>
       </c>
       <c r="T34" t="n">
-        <v>25257690.605173</v>
+        <v>25234233.891642</v>
       </c>
       <c r="U34" t="n">
-        <v>25451397.422822</v>
+        <v>25426638.141472</v>
       </c>
       <c r="V34" t="n">
-        <v>25540083.577819</v>
+        <v>25513919.119741</v>
       </c>
     </row>
     <row r="35">
@@ -3034,58 +3034,58 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>92200.163973</v>
+        <v>92203.19901900001</v>
       </c>
       <c r="F35" t="n">
-        <v>95754.981142</v>
+        <v>95760.082981</v>
       </c>
       <c r="G35" t="n">
-        <v>106760.807543</v>
+        <v>106771.935288</v>
       </c>
       <c r="H35" t="n">
-        <v>118713.215654</v>
+        <v>118736.348037</v>
       </c>
       <c r="I35" t="n">
-        <v>134513.744656</v>
+        <v>134554.234845</v>
       </c>
       <c r="J35" t="n">
-        <v>151555.23848</v>
+        <v>151616.81162</v>
       </c>
       <c r="K35" t="n">
-        <v>163289.142324</v>
+        <v>163371.499133</v>
       </c>
       <c r="L35" t="n">
-        <v>173729.86958</v>
+        <v>173832.970075</v>
       </c>
       <c r="M35" t="n">
-        <v>185496.214676</v>
+        <v>185621.808655</v>
       </c>
       <c r="N35" t="n">
-        <v>199173.128176</v>
+        <v>199324.224129</v>
       </c>
       <c r="O35" t="n">
-        <v>213885.634059</v>
+        <v>214061.995333</v>
       </c>
       <c r="P35" t="n">
-        <v>227130.483054</v>
+        <v>227330.546452</v>
       </c>
       <c r="Q35" t="n">
-        <v>237657.635317</v>
+        <v>237880.333372</v>
       </c>
       <c r="R35" t="n">
-        <v>244137.707844</v>
+        <v>244382.614249</v>
       </c>
       <c r="S35" t="n">
-        <v>245884.909421</v>
+        <v>246150.778691</v>
       </c>
       <c r="T35" t="n">
-        <v>244248.810966</v>
+        <v>244533.316934</v>
       </c>
       <c r="U35" t="n">
-        <v>241618.75093</v>
+        <v>241918.561273</v>
       </c>
       <c r="V35" t="n">
-        <v>240476.257868</v>
+        <v>240789.319046</v>
       </c>
     </row>
     <row r="36">
@@ -3110,58 +3110,58 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>43798.172687</v>
+        <v>43785.164409</v>
       </c>
       <c r="F36" t="n">
-        <v>36564.305361</v>
+        <v>36547.041772</v>
       </c>
       <c r="G36" t="n">
-        <v>29846.93903</v>
+        <v>29832.273671</v>
       </c>
       <c r="H36" t="n">
-        <v>25672.032306</v>
+        <v>25660.898575</v>
       </c>
       <c r="I36" t="n">
-        <v>24315.276521</v>
+        <v>24306.395326</v>
       </c>
       <c r="J36" t="n">
-        <v>24585.945669</v>
+        <v>24578.150385</v>
       </c>
       <c r="K36" t="n">
-        <v>24733.667323</v>
+        <v>24726.539352</v>
       </c>
       <c r="L36" t="n">
-        <v>25048.084155</v>
+        <v>25041.27303</v>
       </c>
       <c r="M36" t="n">
-        <v>25557.378832</v>
+        <v>25550.767955</v>
       </c>
       <c r="N36" t="n">
-        <v>26170.897224</v>
+        <v>26164.522249</v>
       </c>
       <c r="O36" t="n">
-        <v>26534.35646</v>
+        <v>26528.35378</v>
       </c>
       <c r="P36" t="n">
-        <v>27237.609833</v>
+        <v>27231.503589</v>
       </c>
       <c r="Q36" t="n">
-        <v>28020.344086</v>
+        <v>28013.8431</v>
       </c>
       <c r="R36" t="n">
-        <v>28456.502267</v>
+        <v>28449.66205</v>
       </c>
       <c r="S36" t="n">
-        <v>28095.179267</v>
+        <v>28088.435992</v>
       </c>
       <c r="T36" t="n">
-        <v>26994.608118</v>
+        <v>26988.343442</v>
       </c>
       <c r="U36" t="n">
-        <v>25540.177501</v>
+        <v>25534.478059</v>
       </c>
       <c r="V36" t="n">
-        <v>24200.011633</v>
+        <v>24194.695771</v>
       </c>
     </row>
     <row r="37">
@@ -3186,58 +3186,58 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223676.480668</v>
+        <v>223604.211824</v>
       </c>
       <c r="F37" t="n">
-        <v>166719.601314</v>
+        <v>166636.632446</v>
       </c>
       <c r="G37" t="n">
-        <v>135587.883412</v>
+        <v>135517.701204</v>
       </c>
       <c r="H37" t="n">
-        <v>121661.60298</v>
+        <v>121604.740799</v>
       </c>
       <c r="I37" t="n">
-        <v>121398.5434</v>
+        <v>121348.813545</v>
       </c>
       <c r="J37" t="n">
-        <v>127624.560378</v>
+        <v>127577.623759</v>
       </c>
       <c r="K37" t="n">
-        <v>131613.846184</v>
+        <v>131569.313464</v>
       </c>
       <c r="L37" t="n">
-        <v>135165.645179</v>
+        <v>135123.173181</v>
       </c>
       <c r="M37" t="n">
-        <v>141513.900725</v>
+        <v>141471.887003</v>
       </c>
       <c r="N37" t="n">
-        <v>150190.281246</v>
+        <v>150147.864913</v>
       </c>
       <c r="O37" t="n">
-        <v>157445.383432</v>
+        <v>157403.341858</v>
       </c>
       <c r="P37" t="n">
-        <v>160986.845964</v>
+        <v>160947.033315</v>
       </c>
       <c r="Q37" t="n">
-        <v>162179.618532</v>
+        <v>162142.736068</v>
       </c>
       <c r="R37" t="n">
-        <v>162707.849876</v>
+        <v>162673.123705</v>
       </c>
       <c r="S37" t="n">
-        <v>162891.967466</v>
+        <v>162857.99555</v>
       </c>
       <c r="T37" t="n">
-        <v>162628.967038</v>
+        <v>162594.237478</v>
       </c>
       <c r="U37" t="n">
-        <v>161710.098463</v>
+        <v>161673.309909</v>
       </c>
       <c r="V37" t="n">
-        <v>160849.503802</v>
+        <v>160809.449332</v>
       </c>
     </row>
     <row r="38">
@@ -3262,58 +3262,58 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>236857.559797</v>
+        <v>236959.038713</v>
       </c>
       <c r="F38" t="n">
-        <v>204287.808853</v>
+        <v>204466.571167</v>
       </c>
       <c r="G38" t="n">
-        <v>187858.313734</v>
+        <v>188112.319668</v>
       </c>
       <c r="H38" t="n">
-        <v>190886.389146</v>
+        <v>191220.426916</v>
       </c>
       <c r="I38" t="n">
-        <v>216474.034066</v>
+        <v>216912.77311</v>
       </c>
       <c r="J38" t="n">
-        <v>260364.185875</v>
+        <v>260931.7339</v>
       </c>
       <c r="K38" t="n">
-        <v>308038.828373</v>
+        <v>308730.555193</v>
       </c>
       <c r="L38" t="n">
-        <v>360219.097541</v>
+        <v>361036.185543</v>
       </c>
       <c r="M38" t="n">
-        <v>417539.450105</v>
+        <v>418493.553706</v>
       </c>
       <c r="N38" t="n">
-        <v>479103.949223</v>
+        <v>480213.392</v>
       </c>
       <c r="O38" t="n">
-        <v>535682.51348</v>
+        <v>536950.999631</v>
       </c>
       <c r="P38" t="n">
-        <v>582319.112176</v>
+        <v>583739.899188</v>
       </c>
       <c r="Q38" t="n">
-        <v>619823.199587</v>
+        <v>621390.367551</v>
       </c>
       <c r="R38" t="n">
-        <v>649347.332034</v>
+        <v>651055.838782</v>
       </c>
       <c r="S38" t="n">
-        <v>669580.275916</v>
+        <v>671419.978946</v>
       </c>
       <c r="T38" t="n">
-        <v>680591.405623</v>
+        <v>682550.0404309999</v>
       </c>
       <c r="U38" t="n">
-        <v>683163.110235</v>
+        <v>685228.409459</v>
       </c>
       <c r="V38" t="n">
-        <v>681883.084146</v>
+        <v>684055.35225</v>
       </c>
     </row>
     <row r="39">
@@ -3338,58 +3338,58 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>920194.977913</v>
+        <v>919862.560232</v>
       </c>
       <c r="F39" t="n">
-        <v>751298.437394</v>
+        <v>750860.235317</v>
       </c>
       <c r="G39" t="n">
-        <v>693593.814974</v>
+        <v>693135.532375</v>
       </c>
       <c r="H39" t="n">
-        <v>711537.971727</v>
+        <v>711059.465779</v>
       </c>
       <c r="I39" t="n">
-        <v>817322.057976</v>
+        <v>816767.226853</v>
       </c>
       <c r="J39" t="n">
-        <v>993000.670835</v>
+        <v>992303.604945</v>
       </c>
       <c r="K39" t="n">
-        <v>1183092.904753</v>
+        <v>1182219.595743</v>
       </c>
       <c r="L39" t="n">
-        <v>1390186.353646</v>
+        <v>1389104.2655</v>
       </c>
       <c r="M39" t="n">
-        <v>1617200.152659</v>
+        <v>1615879.613421</v>
       </c>
       <c r="N39" t="n">
-        <v>1860300.851025</v>
+        <v>1858717.799966</v>
       </c>
       <c r="O39" t="n">
-        <v>2087026.544028</v>
+        <v>2085184.447978</v>
       </c>
       <c r="P39" t="n">
-        <v>2282298.617187</v>
+        <v>2280212.89207</v>
       </c>
       <c r="Q39" t="n">
-        <v>2451933.672903</v>
+        <v>2449610.564682</v>
       </c>
       <c r="R39" t="n">
-        <v>2599836.216171</v>
+        <v>2597274.339434</v>
       </c>
       <c r="S39" t="n">
-        <v>2717757.299553</v>
+        <v>2714962.020153</v>
       </c>
       <c r="T39" t="n">
-        <v>2802367.131815</v>
+        <v>2799346.747017</v>
       </c>
       <c r="U39" t="n">
-        <v>2854292.179049</v>
+        <v>2851054.666529</v>
       </c>
       <c r="V39" t="n">
-        <v>2891557.013402</v>
+        <v>2888090.231952</v>
       </c>
     </row>
     <row r="40">
@@ -3414,58 +3414,58 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>140604.87065</v>
+        <v>140554.810872</v>
       </c>
       <c r="F40" t="n">
-        <v>120790.323663</v>
+        <v>120720.573311</v>
       </c>
       <c r="G40" t="n">
-        <v>112450.649677</v>
+        <v>112377.238852</v>
       </c>
       <c r="H40" t="n">
-        <v>112142.579179</v>
+        <v>112068.839797</v>
       </c>
       <c r="I40" t="n">
-        <v>124050.472065</v>
+        <v>123969.302961</v>
       </c>
       <c r="J40" t="n">
-        <v>143530.453869</v>
+        <v>143434.95972</v>
       </c>
       <c r="K40" t="n">
-        <v>163460.169442</v>
+        <v>163347.425762</v>
       </c>
       <c r="L40" t="n">
-        <v>186538.639931</v>
+        <v>186404.066973</v>
       </c>
       <c r="M40" t="n">
-        <v>216004.364569</v>
+        <v>215841.0523</v>
       </c>
       <c r="N40" t="n">
-        <v>252837.442332</v>
+        <v>252637.394577</v>
       </c>
       <c r="O40" t="n">
-        <v>292412.785998</v>
+        <v>292171.108901</v>
       </c>
       <c r="P40" t="n">
-        <v>330815.979791</v>
+        <v>330530.699263</v>
       </c>
       <c r="Q40" t="n">
-        <v>366473.266248</v>
+        <v>366143.318956</v>
       </c>
       <c r="R40" t="n">
-        <v>398098.653683</v>
+        <v>397723.733942</v>
       </c>
       <c r="S40" t="n">
-        <v>423385.496359</v>
+        <v>422967.472489</v>
       </c>
       <c r="T40" t="n">
-        <v>441517.474528</v>
+        <v>441059.140267</v>
       </c>
       <c r="U40" t="n">
-        <v>452770.66994</v>
+        <v>452274.766071</v>
       </c>
       <c r="V40" t="n">
-        <v>460439.379111</v>
+        <v>459905.230673</v>
       </c>
     </row>
     <row r="41">
@@ -3490,58 +3490,58 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>165495.965914</v>
+        <v>165440.402117</v>
       </c>
       <c r="F41" t="n">
-        <v>156375.45118</v>
+        <v>156289.68182</v>
       </c>
       <c r="G41" t="n">
-        <v>149458.900129</v>
+        <v>149366.987159</v>
       </c>
       <c r="H41" t="n">
-        <v>151036.59073</v>
+        <v>150944.192699</v>
       </c>
       <c r="I41" t="n">
-        <v>163251.139903</v>
+        <v>163153.887358</v>
       </c>
       <c r="J41" t="n">
-        <v>183422.414628</v>
+        <v>183313.629404</v>
       </c>
       <c r="K41" t="n">
-        <v>202404.897889</v>
+        <v>202282.575952</v>
       </c>
       <c r="L41" t="n">
-        <v>223382.940751</v>
+        <v>223243.660532</v>
       </c>
       <c r="M41" t="n">
-        <v>247633.422705</v>
+        <v>247473.901891</v>
       </c>
       <c r="N41" t="n">
-        <v>274569.121498</v>
+        <v>274387.037665</v>
       </c>
       <c r="O41" t="n">
-        <v>298648.880796</v>
+        <v>298445.834567</v>
       </c>
       <c r="P41" t="n">
-        <v>317091.656749</v>
+        <v>316871.117805</v>
       </c>
       <c r="Q41" t="n">
-        <v>330448.817517</v>
+        <v>330213.493303</v>
       </c>
       <c r="R41" t="n">
-        <v>339477.028469</v>
+        <v>339228.734642</v>
       </c>
       <c r="S41" t="n">
-        <v>343688.270183</v>
+        <v>343429.131272</v>
       </c>
       <c r="T41" t="n">
-        <v>343400.031867</v>
+        <v>343131.901036</v>
       </c>
       <c r="U41" t="n">
-        <v>339287.60111</v>
+        <v>339011.84563</v>
       </c>
       <c r="V41" t="n">
-        <v>333799.365728</v>
+        <v>333515.457105</v>
       </c>
     </row>
     <row r="42">
@@ -3566,58 +3566,58 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8756.506665000001</v>
+        <v>8769.322298999999</v>
       </c>
       <c r="F42" t="n">
-        <v>6899.240957</v>
+        <v>6920.241258</v>
       </c>
       <c r="G42" t="n">
-        <v>5629.391876</v>
+        <v>5656.489646</v>
       </c>
       <c r="H42" t="n">
-        <v>4983.004719</v>
+        <v>5015.863334</v>
       </c>
       <c r="I42" t="n">
-        <v>4965.78323</v>
+        <v>5006.483263</v>
       </c>
       <c r="J42" t="n">
-        <v>5282.210138</v>
+        <v>5332.768165</v>
       </c>
       <c r="K42" t="n">
-        <v>5546.457024</v>
+        <v>5606.307515</v>
       </c>
       <c r="L42" t="n">
-        <v>5781.18286</v>
+        <v>5850.254351</v>
       </c>
       <c r="M42" t="n">
-        <v>6052.870881</v>
+        <v>6132.017607</v>
       </c>
       <c r="N42" t="n">
-        <v>6388.729781</v>
+        <v>6479.343797</v>
       </c>
       <c r="O42" t="n">
-        <v>6687.620194</v>
+        <v>6789.747693</v>
       </c>
       <c r="P42" t="n">
-        <v>6904.903937</v>
+        <v>7017.748702</v>
       </c>
       <c r="Q42" t="n">
-        <v>7060.182123</v>
+        <v>7183.100269</v>
       </c>
       <c r="R42" t="n">
-        <v>7169.042165</v>
+        <v>7301.532299</v>
       </c>
       <c r="S42" t="n">
-        <v>7219.1002</v>
+        <v>7360.346142</v>
       </c>
       <c r="T42" t="n">
-        <v>7214.361835</v>
+        <v>7363.475153</v>
       </c>
       <c r="U42" t="n">
-        <v>7162.439327</v>
+        <v>7318.554335</v>
       </c>
       <c r="V42" t="n">
-        <v>7109.473264</v>
+        <v>7272.714349</v>
       </c>
     </row>
     <row r="43">
@@ -3642,58 +3642,58 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>409879.935799</v>
+        <v>409726.219418</v>
       </c>
       <c r="F43" t="n">
-        <v>476788.924902</v>
+        <v>476489.93133</v>
       </c>
       <c r="G43" t="n">
-        <v>560210.182663</v>
+        <v>559799.411679</v>
       </c>
       <c r="H43" t="n">
-        <v>660671.540934</v>
+        <v>660166.794894</v>
       </c>
       <c r="I43" t="n">
-        <v>818849.075184</v>
+        <v>818210.704561</v>
       </c>
       <c r="J43" t="n">
-        <v>1040080.156849</v>
+        <v>1039242.693808</v>
       </c>
       <c r="K43" t="n">
-        <v>1284650.384105</v>
+        <v>1283570.413663</v>
       </c>
       <c r="L43" t="n">
-        <v>1572527.832104</v>
+        <v>1571144.322678</v>
       </c>
       <c r="M43" t="n">
-        <v>1932226.896761</v>
+        <v>1930452.038499</v>
       </c>
       <c r="N43" t="n">
-        <v>2382832.117328</v>
+        <v>2380554.53211</v>
       </c>
       <c r="O43" t="n">
-        <v>2887135.270345</v>
+        <v>2884269.166928</v>
       </c>
       <c r="P43" t="n">
-        <v>3403478.799695</v>
+        <v>3399971.862926</v>
       </c>
       <c r="Q43" t="n">
-        <v>3908360.103764</v>
+        <v>3904174.547699</v>
       </c>
       <c r="R43" t="n">
-        <v>4380939.429615</v>
+        <v>4376050.372405</v>
       </c>
       <c r="S43" t="n">
-        <v>4785270.476547</v>
+        <v>4779689.08972</v>
       </c>
       <c r="T43" t="n">
-        <v>5099919.271991</v>
+        <v>5093681.261296</v>
       </c>
       <c r="U43" t="n">
-        <v>5316754.94036</v>
+        <v>5309909.153725</v>
       </c>
       <c r="V43" t="n">
-        <v>5466788.924678</v>
+        <v>5459349.274271</v>
       </c>
     </row>
     <row r="44">
@@ -3718,58 +3718,58 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>186421.223879</v>
+        <v>186466.37308</v>
       </c>
       <c r="F44" t="n">
-        <v>177987.008826</v>
+        <v>178071.620938</v>
       </c>
       <c r="G44" t="n">
-        <v>175712.907404</v>
+        <v>175846.339116</v>
       </c>
       <c r="H44" t="n">
-        <v>189064.537116</v>
+        <v>189253.601536</v>
       </c>
       <c r="I44" t="n">
-        <v>225772.107278</v>
+        <v>226032.433576</v>
       </c>
       <c r="J44" t="n">
-        <v>281174.68451</v>
+        <v>281520.253004</v>
       </c>
       <c r="K44" t="n">
-        <v>336412.988003</v>
+        <v>336840.448841</v>
       </c>
       <c r="L44" t="n">
-        <v>383621.567781</v>
+        <v>384132.959407</v>
       </c>
       <c r="M44" t="n">
-        <v>429994.722884</v>
+        <v>430599.53417</v>
       </c>
       <c r="N44" t="n">
-        <v>483467.934969</v>
+        <v>484179.476215</v>
       </c>
       <c r="O44" t="n">
-        <v>543421.3919320001</v>
+        <v>544243.003854</v>
       </c>
       <c r="P44" t="n">
-        <v>606171.964273</v>
+        <v>607099.9510389999</v>
       </c>
       <c r="Q44" t="n">
-        <v>670498.3907</v>
+        <v>671529.274038</v>
       </c>
       <c r="R44" t="n">
-        <v>733854.216677</v>
+        <v>734985.010601</v>
       </c>
       <c r="S44" t="n">
-        <v>790598.985814</v>
+        <v>791823.551619</v>
       </c>
       <c r="T44" t="n">
-        <v>837135.435958</v>
+        <v>838446.121791</v>
       </c>
       <c r="U44" t="n">
-        <v>871850.414454</v>
+        <v>873239.452856</v>
       </c>
       <c r="V44" t="n">
-        <v>899483.245369</v>
+        <v>900951.372659</v>
       </c>
     </row>
     <row r="45">
@@ -3794,58 +3794,58 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>37737.734956</v>
+        <v>37753.157347</v>
       </c>
       <c r="F45" t="n">
-        <v>33052.730496</v>
+        <v>33079.971782</v>
       </c>
       <c r="G45" t="n">
-        <v>30642.586819</v>
+        <v>30681.406482</v>
       </c>
       <c r="H45" t="n">
-        <v>30542.899441</v>
+        <v>30593.917208</v>
       </c>
       <c r="I45" t="n">
-        <v>33015.605242</v>
+        <v>33082.047163</v>
       </c>
       <c r="J45" t="n">
-        <v>37377.161452</v>
+        <v>37461.915429</v>
       </c>
       <c r="K45" t="n">
-        <v>41881.227917</v>
+        <v>41983.008867</v>
       </c>
       <c r="L45" t="n">
-        <v>47149.453091</v>
+        <v>47268.125529</v>
       </c>
       <c r="M45" t="n">
-        <v>53649.329005</v>
+        <v>53786.500373</v>
       </c>
       <c r="N45" t="n">
-        <v>61367.110135</v>
+        <v>61525.412526</v>
       </c>
       <c r="O45" t="n">
-        <v>69015.323711</v>
+        <v>69195.150955</v>
       </c>
       <c r="P45" t="n">
-        <v>75641.39477</v>
+        <v>75841.60042</v>
       </c>
       <c r="Q45" t="n">
-        <v>81034.702252</v>
+        <v>81254.178688</v>
       </c>
       <c r="R45" t="n">
-        <v>85143.112087</v>
+        <v>85380.91623</v>
       </c>
       <c r="S45" t="n">
-        <v>87725.243254</v>
+        <v>87979.757075</v>
       </c>
       <c r="T45" t="n">
-        <v>88849.243428</v>
+        <v>89118.625527</v>
       </c>
       <c r="U45" t="n">
-        <v>88749.776795</v>
+        <v>89032.332649</v>
       </c>
       <c r="V45" t="n">
-        <v>88172.628536</v>
+        <v>88468.50719400001</v>
       </c>
     </row>
     <row r="46">
@@ -3870,58 +3870,58 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>127198.961168</v>
+        <v>127245.321153</v>
       </c>
       <c r="F46" t="n">
-        <v>124914.164204</v>
+        <v>125000.452157</v>
       </c>
       <c r="G46" t="n">
-        <v>131262.146202</v>
+        <v>131394.310146</v>
       </c>
       <c r="H46" t="n">
-        <v>144410.591538</v>
+        <v>144598.490349</v>
       </c>
       <c r="I46" t="n">
-        <v>172447.160848</v>
+        <v>172711.0899</v>
       </c>
       <c r="J46" t="n">
-        <v>215698.345119</v>
+        <v>216058.947763</v>
       </c>
       <c r="K46" t="n">
-        <v>264900.384691</v>
+        <v>265361.093776</v>
       </c>
       <c r="L46" t="n">
-        <v>323288.013947</v>
+        <v>323855.502756</v>
       </c>
       <c r="M46" t="n">
-        <v>394011.700279</v>
+        <v>394700.762991</v>
       </c>
       <c r="N46" t="n">
-        <v>479214.178898</v>
+        <v>480044.80955</v>
       </c>
       <c r="O46" t="n">
-        <v>572736.428467</v>
+        <v>573717.771505</v>
       </c>
       <c r="P46" t="n">
-        <v>670900.357782</v>
+        <v>672032.505891</v>
       </c>
       <c r="Q46" t="n">
-        <v>774434.78984</v>
+        <v>775716.720795</v>
       </c>
       <c r="R46" t="n">
-        <v>883327.584266</v>
+        <v>884757.091011</v>
       </c>
       <c r="S46" t="n">
-        <v>990275.625616</v>
+        <v>991845.040884</v>
       </c>
       <c r="T46" t="n">
-        <v>1090505.712613</v>
+        <v>1092204.379028</v>
       </c>
       <c r="U46" t="n">
-        <v>1180531.469845</v>
+        <v>1182348.048208</v>
       </c>
       <c r="V46" t="n">
-        <v>1265270.552669</v>
+        <v>1267204.260082</v>
       </c>
     </row>
     <row r="47">
@@ -3946,58 +3946,58 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1590116.793584</v>
+        <v>1591135.341775</v>
       </c>
       <c r="F47" t="n">
-        <v>1560213.112087</v>
+        <v>1561990.914281</v>
       </c>
       <c r="G47" t="n">
-        <v>1535914.332551</v>
+        <v>1538455.272299</v>
       </c>
       <c r="H47" t="n">
-        <v>1601613.182761</v>
+        <v>1605013.36862</v>
       </c>
       <c r="I47" t="n">
-        <v>1825230.27058</v>
+        <v>1829797.723072</v>
       </c>
       <c r="J47" t="n">
-        <v>2186496.664123</v>
+        <v>2192563.020953</v>
       </c>
       <c r="K47" t="n">
-        <v>2562786.268706</v>
+        <v>2570397.814859</v>
       </c>
       <c r="L47" t="n">
-        <v>2960007.936957</v>
+        <v>2969269.149255</v>
       </c>
       <c r="M47" t="n">
-        <v>3383287.952083</v>
+        <v>3394416.300059</v>
       </c>
       <c r="N47" t="n">
-        <v>3821399.776062</v>
+        <v>3834680.98556</v>
       </c>
       <c r="O47" t="n">
-        <v>4198041.319877</v>
+        <v>4213574.607243</v>
       </c>
       <c r="P47" t="n">
-        <v>4479974.476625</v>
+        <v>4497723.552102</v>
       </c>
       <c r="Q47" t="n">
-        <v>4685698.36429</v>
+        <v>4705639.703621</v>
       </c>
       <c r="R47" t="n">
-        <v>4835851.282208</v>
+        <v>4857982.31287</v>
       </c>
       <c r="S47" t="n">
-        <v>4929723.605578</v>
+        <v>4953984.25279</v>
       </c>
       <c r="T47" t="n">
-        <v>4974172.193275</v>
+        <v>5000479.110699</v>
       </c>
       <c r="U47" t="n">
-        <v>4978697.784172</v>
+        <v>5006974.249005</v>
       </c>
       <c r="V47" t="n">
-        <v>4977856.428408</v>
+        <v>5008201.816488</v>
       </c>
     </row>
     <row r="48">
@@ -4022,58 +4022,58 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>93852.63054</v>
+        <v>93923.687874</v>
       </c>
       <c r="F48" t="n">
-        <v>83356.005704</v>
+        <v>83476.103168</v>
       </c>
       <c r="G48" t="n">
-        <v>78887.55080700001</v>
+        <v>79050.917613</v>
       </c>
       <c r="H48" t="n">
-        <v>78488.024623</v>
+        <v>78695.832689</v>
       </c>
       <c r="I48" t="n">
-        <v>84739.47582599999</v>
+        <v>85004.919629</v>
       </c>
       <c r="J48" t="n">
-        <v>95370.487666</v>
+        <v>95705.431964</v>
       </c>
       <c r="K48" t="n">
-        <v>105480.963492</v>
+        <v>105880.488018</v>
       </c>
       <c r="L48" t="n">
-        <v>116462.937269</v>
+        <v>116926.40231</v>
       </c>
       <c r="M48" t="n">
-        <v>129040.472772</v>
+        <v>129573.589735</v>
       </c>
       <c r="N48" t="n">
-        <v>143145.977386</v>
+        <v>143757.829667</v>
       </c>
       <c r="O48" t="n">
-        <v>156458.507658</v>
+        <v>157150.589483</v>
       </c>
       <c r="P48" t="n">
-        <v>169302.644271</v>
+        <v>170072.370729</v>
       </c>
       <c r="Q48" t="n">
-        <v>181909.141266</v>
+        <v>182755.075689</v>
       </c>
       <c r="R48" t="n">
-        <v>193797.138269</v>
+        <v>194718.253379</v>
       </c>
       <c r="S48" t="n">
-        <v>203348.479994</v>
+        <v>204340.40616</v>
       </c>
       <c r="T48" t="n">
-        <v>209981.370977</v>
+        <v>211038.503208</v>
       </c>
       <c r="U48" t="n">
-        <v>213765.128318</v>
+        <v>214882.133258</v>
       </c>
       <c r="V48" t="n">
-        <v>216291.47319</v>
+        <v>217470.415434</v>
       </c>
     </row>
     <row r="49">
@@ -4098,58 +4098,58 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>557573.654176</v>
+        <v>557376.585289</v>
       </c>
       <c r="F49" t="n">
-        <v>517728.095855</v>
+        <v>517428.952841</v>
       </c>
       <c r="G49" t="n">
-        <v>499121.325451</v>
+        <v>498794.464749</v>
       </c>
       <c r="H49" t="n">
-        <v>506176.146103</v>
+        <v>505842.455068</v>
       </c>
       <c r="I49" t="n">
-        <v>558545.718416</v>
+        <v>558181.370002</v>
       </c>
       <c r="J49" t="n">
-        <v>636163.047915</v>
+        <v>635745.289183</v>
       </c>
       <c r="K49" t="n">
-        <v>713885.753756</v>
+        <v>713404.311036</v>
       </c>
       <c r="L49" t="n">
-        <v>808881.058546</v>
+        <v>808314.1647589999</v>
       </c>
       <c r="M49" t="n">
-        <v>938954.057434</v>
+        <v>938266.1900450001</v>
       </c>
       <c r="N49" t="n">
-        <v>1107683.04957</v>
+        <v>1106834.164235</v>
       </c>
       <c r="O49" t="n">
-        <v>1292467.754372</v>
+        <v>1291432.372335</v>
       </c>
       <c r="P49" t="n">
-        <v>1472290.036588</v>
+        <v>1471058.465337</v>
       </c>
       <c r="Q49" t="n">
-        <v>1637277.229605</v>
+        <v>1635846.715115</v>
       </c>
       <c r="R49" t="n">
-        <v>1780723.41679</v>
+        <v>1779095.789212</v>
       </c>
       <c r="S49" t="n">
-        <v>1892226.905649</v>
+        <v>1890413.985491</v>
       </c>
       <c r="T49" t="n">
-        <v>1968759.598652</v>
+        <v>1966776.96751</v>
       </c>
       <c r="U49" t="n">
-        <v>2012449.263683</v>
+        <v>2010311.625865</v>
       </c>
       <c r="V49" t="n">
-        <v>2038858.424871</v>
+        <v>2036565.036093</v>
       </c>
     </row>
     <row r="50">
@@ -4174,58 +4174,58 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>14909.787962</v>
+        <v>14904.827207</v>
       </c>
       <c r="F50" t="n">
-        <v>12258.038805</v>
+        <v>12251.501852</v>
       </c>
       <c r="G50" t="n">
-        <v>10126.90819</v>
+        <v>10121.047608</v>
       </c>
       <c r="H50" t="n">
-        <v>8845.284118</v>
+        <v>8840.443133000001</v>
       </c>
       <c r="I50" t="n">
-        <v>8530.843535</v>
+        <v>8526.534764</v>
       </c>
       <c r="J50" t="n">
-        <v>8774.096055</v>
+        <v>8769.872971999999</v>
       </c>
       <c r="K50" t="n">
-        <v>8986.113426</v>
+        <v>8981.839728000001</v>
       </c>
       <c r="L50" t="n">
-        <v>9301.157196</v>
+        <v>9296.676148</v>
       </c>
       <c r="M50" t="n">
-        <v>9859.736774999999</v>
+        <v>9854.842608000001</v>
       </c>
       <c r="N50" t="n">
-        <v>10648.937433</v>
+        <v>10643.441711</v>
       </c>
       <c r="O50" t="n">
-        <v>11477.835174</v>
+        <v>11471.652951</v>
       </c>
       <c r="P50" t="n">
-        <v>12235.936195</v>
+        <v>12229.034504</v>
       </c>
       <c r="Q50" t="n">
-        <v>12942.899651</v>
+        <v>12935.214485</v>
       </c>
       <c r="R50" t="n">
-        <v>13632.192811</v>
+        <v>13623.613038</v>
       </c>
       <c r="S50" t="n">
-        <v>14232.181651</v>
+        <v>14222.642182</v>
       </c>
       <c r="T50" t="n">
-        <v>14987.699316</v>
+        <v>14976.840005</v>
       </c>
       <c r="U50" t="n">
-        <v>15709.923927</v>
+        <v>15697.556089</v>
       </c>
       <c r="V50" t="n">
-        <v>16290.770443</v>
+        <v>16276.860101</v>
       </c>
     </row>
     <row r="51">
@@ -4250,58 +4250,58 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>148430.270828</v>
+        <v>148465.066688</v>
       </c>
       <c r="F51" t="n">
-        <v>123299.200794</v>
+        <v>123369.401088</v>
       </c>
       <c r="G51" t="n">
-        <v>110528.261395</v>
+        <v>110638.20684</v>
       </c>
       <c r="H51" t="n">
-        <v>106861.820476</v>
+        <v>107014.505814</v>
       </c>
       <c r="I51" t="n">
-        <v>115444.403397</v>
+        <v>115650.681699</v>
       </c>
       <c r="J51" t="n">
-        <v>132992.18485</v>
+        <v>133263.182454</v>
       </c>
       <c r="K51" t="n">
-        <v>152182.439316</v>
+        <v>152516.723718</v>
       </c>
       <c r="L51" t="n">
-        <v>174661.450568</v>
+        <v>175061.080963</v>
       </c>
       <c r="M51" t="n">
-        <v>202162.808074</v>
+        <v>202635.474465</v>
       </c>
       <c r="N51" t="n">
-        <v>235548.871442</v>
+        <v>236105.712994</v>
       </c>
       <c r="O51" t="n">
-        <v>271066.426753</v>
+        <v>271711.407973</v>
       </c>
       <c r="P51" t="n">
-        <v>305917.919162</v>
+        <v>306649.676772</v>
       </c>
       <c r="Q51" t="n">
-        <v>342363.822697</v>
+        <v>343181.828515</v>
       </c>
       <c r="R51" t="n">
-        <v>380219.309975</v>
+        <v>381123.347528</v>
       </c>
       <c r="S51" t="n">
-        <v>416533.291605</v>
+        <v>417519.858532</v>
       </c>
       <c r="T51" t="n">
-        <v>448085.946985</v>
+        <v>449149.67547</v>
       </c>
       <c r="U51" t="n">
-        <v>473276.467098</v>
+        <v>474411.588269</v>
       </c>
       <c r="V51" t="n">
-        <v>494286.140176</v>
+        <v>495493.870094</v>
       </c>
     </row>
     <row r="52">
@@ -4326,58 +4326,58 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>153394.415395</v>
+        <v>153367.258432</v>
       </c>
       <c r="F52" t="n">
-        <v>117349.811167</v>
+        <v>117325.470112</v>
       </c>
       <c r="G52" t="n">
-        <v>95906.579855</v>
+        <v>95898.51774900001</v>
       </c>
       <c r="H52" t="n">
-        <v>86755.12139299999</v>
+        <v>86763.301318</v>
       </c>
       <c r="I52" t="n">
-        <v>90150.796153</v>
+        <v>90172.558974</v>
       </c>
       <c r="J52" t="n">
-        <v>104109.446921</v>
+        <v>104141.737834</v>
       </c>
       <c r="K52" t="n">
-        <v>121766.113816</v>
+        <v>121804.979576</v>
       </c>
       <c r="L52" t="n">
-        <v>143070.290536</v>
+        <v>143112.890813</v>
       </c>
       <c r="M52" t="n">
-        <v>167967.769181</v>
+        <v>168012.887556</v>
       </c>
       <c r="N52" t="n">
-        <v>197850.477345</v>
+        <v>197896.854841</v>
       </c>
       <c r="O52" t="n">
-        <v>230826.35995</v>
+        <v>230871.05818</v>
       </c>
       <c r="P52" t="n">
-        <v>265959.702157</v>
+        <v>265998.190765</v>
       </c>
       <c r="Q52" t="n">
-        <v>303969.931751</v>
+        <v>303996.43868</v>
       </c>
       <c r="R52" t="n">
-        <v>345546.078485</v>
+        <v>345553.249733</v>
       </c>
       <c r="S52" t="n">
-        <v>388057.590943</v>
+        <v>388038.070417</v>
       </c>
       <c r="T52" t="n">
-        <v>428601.439982</v>
+        <v>428548.834135</v>
       </c>
       <c r="U52" t="n">
-        <v>464717.630944</v>
+        <v>464627.009563</v>
       </c>
       <c r="V52" t="n">
-        <v>496738.904856</v>
+        <v>496606.798607</v>
       </c>
     </row>
     <row r="53">
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>251795.677058</v>
+        <v>251795.672866</v>
       </c>
       <c r="F54" t="n">
-        <v>378196.885838</v>
+        <v>378196.867392</v>
       </c>
       <c r="G54" t="n">
-        <v>541606.649797</v>
+        <v>541606.5868310001</v>
       </c>
       <c r="H54" t="n">
-        <v>775595.1283559999</v>
+        <v>775594.911011</v>
       </c>
       <c r="I54" t="n">
-        <v>1187703.293334</v>
+        <v>1187702.235134</v>
       </c>
       <c r="J54" t="n">
         <v>2958539.24963</v>
@@ -4526,7 +4526,7 @@
         <v>10628975.970894</v>
       </c>
       <c r="U54" t="n">
-        <v>10829134.730753</v>
+        <v>10829134.730754</v>
       </c>
       <c r="V54" t="n">
         <v>10906487.984996</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>255115.677542</v>
+        <v>255115.681734</v>
       </c>
       <c r="F55" t="n">
-        <v>356462.948499</v>
+        <v>356462.966945</v>
       </c>
       <c r="G55" t="n">
-        <v>483629.476544</v>
+        <v>483629.539509</v>
       </c>
       <c r="H55" t="n">
-        <v>667003.293531</v>
+        <v>667003.5108770001</v>
       </c>
       <c r="I55" t="n">
-        <v>995617.934241</v>
+        <v>995618.992441</v>
       </c>
       <c r="J55" t="n">
         <v>151073.676652</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>9.076506</v>
+        <v>8.447108999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>23.159882</v>
+        <v>21.555333</v>
       </c>
       <c r="G58" t="n">
-        <v>53.029154</v>
+        <v>49.360226</v>
       </c>
       <c r="H58" t="n">
-        <v>125.333267</v>
+        <v>116.684227</v>
       </c>
       <c r="I58" t="n">
-        <v>393.816277</v>
+        <v>366.842634</v>
       </c>
       <c r="J58" t="n">
         <v>37820.89199</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2.795379</v>
+        <v>2.601538</v>
       </c>
       <c r="F59" t="n">
-        <v>7.682262</v>
+        <v>7.150024</v>
       </c>
       <c r="G59" t="n">
-        <v>18.795311</v>
+        <v>17.49492</v>
       </c>
       <c r="H59" t="n">
-        <v>45.688843</v>
+        <v>42.535932</v>
       </c>
       <c r="I59" t="n">
-        <v>144.889639</v>
+        <v>134.965718</v>
       </c>
       <c r="J59" t="n">
         <v>13930.663508</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.96864</v>
+        <v>4.624097</v>
       </c>
       <c r="F60" t="n">
-        <v>10.387711</v>
+        <v>9.668035</v>
       </c>
       <c r="G60" t="n">
-        <v>19.85576</v>
+        <v>18.481999</v>
       </c>
       <c r="H60" t="n">
-        <v>41.919459</v>
+        <v>39.026667</v>
       </c>
       <c r="I60" t="n">
-        <v>124.577763</v>
+        <v>116.045063</v>
       </c>
       <c r="J60" t="n">
         <v>11684.274866</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>97202.602635</v>
+        <v>97203.50046</v>
       </c>
       <c r="F61" t="n">
-        <v>102969.425266</v>
+        <v>102971.296646</v>
       </c>
       <c r="G61" t="n">
-        <v>117563.034928</v>
+        <v>117565.85875</v>
       </c>
       <c r="H61" t="n">
-        <v>137509.331482</v>
+        <v>137512.945916</v>
       </c>
       <c r="I61" t="n">
-        <v>172630.696353</v>
+        <v>172633.815435</v>
       </c>
       <c r="J61" t="n">
         <v>225016.74501</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>55568.410926</v>
+        <v>55561.56077</v>
       </c>
       <c r="F62" t="n">
-        <v>60488.456791</v>
+        <v>60469.822366</v>
       </c>
       <c r="G62" t="n">
-        <v>69380.624041</v>
+        <v>69337.71946399999</v>
       </c>
       <c r="H62" t="n">
-        <v>80184.599615</v>
+        <v>80085.83253299999</v>
       </c>
       <c r="I62" t="n">
-        <v>99407.671527</v>
+        <v>99111.34338200001</v>
       </c>
       <c r="J62" t="n">
         <v>511326.475718</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>34243.454402</v>
+        <v>34237.625458</v>
       </c>
       <c r="F63" t="n">
-        <v>37038.92697</v>
+        <v>37023.185715</v>
       </c>
       <c r="G63" t="n">
-        <v>42542.485966</v>
+        <v>42506.32166</v>
       </c>
       <c r="H63" t="n">
-        <v>50894.296735</v>
+        <v>50808.701204</v>
       </c>
       <c r="I63" t="n">
-        <v>67364.277993</v>
+        <v>67093.852709</v>
       </c>
       <c r="J63" t="n">
         <v>467702.063748</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1.109247</v>
+        <v>1.032328</v>
       </c>
       <c r="F64" t="n">
-        <v>2.553103</v>
+        <v>2.37622</v>
       </c>
       <c r="G64" t="n">
-        <v>5.433185</v>
+        <v>5.057279</v>
       </c>
       <c r="H64" t="n">
-        <v>12.254685</v>
+        <v>11.409009</v>
       </c>
       <c r="I64" t="n">
-        <v>37.676172</v>
+        <v>35.09562</v>
       </c>
       <c r="J64" t="n">
         <v>3584.385025</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>295486.854931</v>
+        <v>295494.002921</v>
       </c>
       <c r="F65" t="n">
-        <v>341953.304615</v>
+        <v>341972.297422</v>
       </c>
       <c r="G65" t="n">
-        <v>427864.12211</v>
+        <v>427906.375795</v>
       </c>
       <c r="H65" t="n">
-        <v>539683.062479</v>
+        <v>539777.666428</v>
       </c>
       <c r="I65" t="n">
-        <v>719376.701056</v>
+        <v>719654.439106</v>
       </c>
       <c r="J65" t="n">
         <v>598453.933881</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>104359.226973</v>
+        <v>104362.037495</v>
       </c>
       <c r="F66" t="n">
-        <v>119972.399051</v>
+        <v>119979.877859</v>
       </c>
       <c r="G66" t="n">
-        <v>150664.992641</v>
+        <v>150681.91041</v>
       </c>
       <c r="H66" t="n">
-        <v>191978.535645</v>
+        <v>192017.37047</v>
       </c>
       <c r="I66" t="n">
-        <v>259364.942336</v>
+        <v>259482.460321</v>
       </c>
       <c r="J66" t="n">
         <v>193589.289989</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>123802.148515</v>
+        <v>123806.975155</v>
       </c>
       <c r="F67" t="n">
-        <v>144067.194222</v>
+        <v>144080.481443</v>
       </c>
       <c r="G67" t="n">
-        <v>191834.983551</v>
+        <v>191867.91281</v>
       </c>
       <c r="H67" t="n">
-        <v>263715.345909</v>
+        <v>263799.785964</v>
       </c>
       <c r="I67" t="n">
-        <v>383474.256619</v>
+        <v>383759.870499</v>
       </c>
       <c r="J67" t="n">
         <v>130531.207208</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>10370.77374</v>
+        <v>10369.604117</v>
       </c>
       <c r="F68" t="n">
-        <v>11662.380898</v>
+        <v>11659.092137</v>
       </c>
       <c r="G68" t="n">
-        <v>15097.775128</v>
+        <v>15089.272191</v>
       </c>
       <c r="H68" t="n">
-        <v>19631.521294</v>
+        <v>19609.598491</v>
       </c>
       <c r="I68" t="n">
-        <v>26471.506595</v>
+        <v>26400.016515</v>
       </c>
       <c r="J68" t="n">
         <v>132648.181254</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2.236755</v>
+        <v>2.08165</v>
       </c>
       <c r="F69" t="n">
-        <v>5.697863</v>
+        <v>5.303107</v>
       </c>
       <c r="G69" t="n">
-        <v>12.765354</v>
+        <v>11.882157</v>
       </c>
       <c r="H69" t="n">
-        <v>29.345546</v>
+        <v>27.320459</v>
       </c>
       <c r="I69" t="n">
-        <v>89.92308199999999</v>
+        <v>83.76398399999999</v>
       </c>
       <c r="J69" t="n">
         <v>8687.302823</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>78735.724703</v>
+        <v>78738.549893</v>
       </c>
       <c r="F70" t="n">
-        <v>86090.813267</v>
+        <v>86098.085649</v>
       </c>
       <c r="G70" t="n">
-        <v>105618.812016</v>
+        <v>105635.303478</v>
       </c>
       <c r="H70" t="n">
-        <v>134025.113579</v>
+        <v>134063.876221</v>
       </c>
       <c r="I70" t="n">
-        <v>182158.760657</v>
+        <v>182280.416</v>
       </c>
       <c r="J70" t="n">
         <v>79388.19121800001</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>33569.543941</v>
+        <v>33568.234958</v>
       </c>
       <c r="F71" t="n">
-        <v>38586.080666</v>
+        <v>38582.198026</v>
       </c>
       <c r="G71" t="n">
-        <v>45010.908767</v>
+        <v>45001.404523</v>
       </c>
       <c r="H71" t="n">
-        <v>52411.578358</v>
+        <v>52388.598351</v>
       </c>
       <c r="I71" t="n">
-        <v>66085.21923800001</v>
+        <v>66011.840346</v>
       </c>
       <c r="J71" t="n">
         <v>189035.97232</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>70666.190952</v>
+        <v>70666.930329</v>
       </c>
       <c r="F72" t="n">
-        <v>70295.912447</v>
+        <v>70297.40054800001</v>
       </c>
       <c r="G72" t="n">
-        <v>78515.738153</v>
+        <v>78518.11450700001</v>
       </c>
       <c r="H72" t="n">
-        <v>91790.728187</v>
+        <v>91794.367853</v>
       </c>
       <c r="I72" t="n">
-        <v>116374.380751</v>
+        <v>116380.628054</v>
       </c>
       <c r="J72" t="n">
         <v>149017.789681</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>559.883425</v>
+        <v>557.26144</v>
       </c>
       <c r="F73" t="n">
-        <v>488.587945</v>
+        <v>483.370349</v>
       </c>
       <c r="G73" t="n">
-        <v>465.299614</v>
+        <v>456.646267</v>
       </c>
       <c r="H73" t="n">
-        <v>546.8795280000001</v>
+        <v>530.864031</v>
       </c>
       <c r="I73" t="n">
-        <v>970.359558</v>
+        <v>927.380797</v>
       </c>
       <c r="J73" t="n">
         <v>55659.948123</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.981332</v>
+        <v>0.913283</v>
       </c>
       <c r="F74" t="n">
-        <v>2.856734</v>
+        <v>2.658816</v>
       </c>
       <c r="G74" t="n">
-        <v>6.659578</v>
+        <v>6.198822</v>
       </c>
       <c r="H74" t="n">
-        <v>15.203135</v>
+        <v>14.153992</v>
       </c>
       <c r="I74" t="n">
-        <v>45.560407</v>
+        <v>42.43984</v>
       </c>
       <c r="J74" t="n">
         <v>4202.641104</v>
@@ -6074,58 +6074,58 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>12297.007955</v>
+        <v>12297.008327</v>
       </c>
       <c r="F75" t="n">
-        <v>13995.035487</v>
+        <v>13995.036216</v>
       </c>
       <c r="G75" t="n">
-        <v>21399.550167</v>
+        <v>21399.550878</v>
       </c>
       <c r="H75" t="n">
-        <v>31980.992615</v>
+        <v>31980.992723</v>
       </c>
       <c r="I75" t="n">
-        <v>45775.004222</v>
+        <v>45775.0032</v>
       </c>
       <c r="J75" t="n">
-        <v>60291.483316</v>
+        <v>60291.480855</v>
       </c>
       <c r="K75" t="n">
-        <v>71878.622825</v>
+        <v>71878.619093</v>
       </c>
       <c r="L75" t="n">
-        <v>81260.43668899999</v>
+        <v>81260.432116</v>
       </c>
       <c r="M75" t="n">
-        <v>87675.591846</v>
+        <v>87675.58673900001</v>
       </c>
       <c r="N75" t="n">
-        <v>93430.398158</v>
+        <v>93430.39257700001</v>
       </c>
       <c r="O75" t="n">
-        <v>104069.869283</v>
+        <v>104069.861988</v>
       </c>
       <c r="P75" t="n">
-        <v>123507.409634</v>
+        <v>123507.397627</v>
       </c>
       <c r="Q75" t="n">
-        <v>133022.113509</v>
+        <v>133022.093349</v>
       </c>
       <c r="R75" t="n">
-        <v>138156.743883</v>
+        <v>138156.710674</v>
       </c>
       <c r="S75" t="n">
-        <v>139350.811616</v>
+        <v>139350.761052</v>
       </c>
       <c r="T75" t="n">
-        <v>140056.757749</v>
+        <v>140056.685686</v>
       </c>
       <c r="U75" t="n">
-        <v>140308.397011</v>
+        <v>140308.295786</v>
       </c>
       <c r="V75" t="n">
-        <v>141999.079019</v>
+        <v>141998.930674</v>
       </c>
     </row>
     <row r="76">
@@ -6150,58 +6150,58 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11141.124207</v>
+        <v>11141.120082</v>
       </c>
       <c r="F76" t="n">
-        <v>12850.621698</v>
+        <v>12850.60792</v>
       </c>
       <c r="G76" t="n">
-        <v>15837.197132</v>
+        <v>15837.167571</v>
       </c>
       <c r="H76" t="n">
-        <v>20056.850104</v>
+        <v>20056.796031</v>
       </c>
       <c r="I76" t="n">
-        <v>26583.069357</v>
+        <v>26582.973521</v>
       </c>
       <c r="J76" t="n">
-        <v>35158.167177</v>
+        <v>35158.001143</v>
       </c>
       <c r="K76" t="n">
-        <v>43887.538642</v>
+        <v>43887.269927</v>
       </c>
       <c r="L76" t="n">
-        <v>52651.128637</v>
+        <v>52650.713697</v>
       </c>
       <c r="M76" t="n">
-        <v>59545.006905</v>
+        <v>59544.411334</v>
       </c>
       <c r="N76" t="n">
-        <v>65684.79846599999</v>
+        <v>65683.971773</v>
       </c>
       <c r="O76" t="n">
-        <v>73808.888158</v>
+        <v>73807.73691599999</v>
       </c>
       <c r="P76" t="n">
-        <v>86487.483452</v>
+        <v>86485.82739599999</v>
       </c>
       <c r="Q76" t="n">
-        <v>90403.270536</v>
+        <v>90401.153829</v>
       </c>
       <c r="R76" t="n">
-        <v>90327.977101</v>
+        <v>90325.381681</v>
       </c>
       <c r="S76" t="n">
-        <v>88079.98749699999</v>
+        <v>88076.83401399999</v>
       </c>
       <c r="T76" t="n">
-        <v>86734.256683</v>
+        <v>86730.29212100001</v>
       </c>
       <c r="U76" t="n">
-        <v>86521.93324</v>
+        <v>86516.718383</v>
       </c>
       <c r="V76" t="n">
-        <v>88097.20337800001</v>
+        <v>88089.887479</v>
       </c>
     </row>
     <row r="77">
@@ -6226,58 +6226,58 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>48973.76073</v>
+        <v>48973.763152</v>
       </c>
       <c r="F77" t="n">
-        <v>63225.280708</v>
+        <v>63225.287289</v>
       </c>
       <c r="G77" t="n">
-        <v>101081.234266</v>
+        <v>101081.248279</v>
       </c>
       <c r="H77" t="n">
-        <v>146165.048209</v>
+        <v>146165.074919</v>
       </c>
       <c r="I77" t="n">
-        <v>193730.92841</v>
+        <v>193730.976563</v>
       </c>
       <c r="J77" t="n">
-        <v>237658.761452</v>
+        <v>237658.840759</v>
       </c>
       <c r="K77" t="n">
-        <v>271740.672667</v>
+        <v>271740.791326</v>
       </c>
       <c r="L77" t="n">
-        <v>303813.302924</v>
+        <v>303813.473322</v>
       </c>
       <c r="M77" t="n">
-        <v>330232.115227</v>
+        <v>330232.350031</v>
       </c>
       <c r="N77" t="n">
-        <v>356784.148508</v>
+        <v>356784.468621</v>
       </c>
       <c r="O77" t="n">
-        <v>402067.974051</v>
+        <v>402068.425959</v>
       </c>
       <c r="P77" t="n">
-        <v>480175.277792</v>
+        <v>480175.951988</v>
       </c>
       <c r="Q77" t="n">
-        <v>518218.466373</v>
+        <v>518219.375943</v>
       </c>
       <c r="R77" t="n">
-        <v>538519.498352</v>
+        <v>538520.686869</v>
       </c>
       <c r="S77" t="n">
-        <v>544118.58868</v>
+        <v>544120.118864</v>
       </c>
       <c r="T77" t="n">
-        <v>548097.461845</v>
+        <v>548099.463699</v>
       </c>
       <c r="U77" t="n">
-        <v>550373.153433</v>
+        <v>550375.8356399999</v>
       </c>
       <c r="V77" t="n">
-        <v>557426.163205</v>
+        <v>557429.932633</v>
       </c>
     </row>
     <row r="78">
@@ -6302,58 +6302,58 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>36686.434426</v>
+        <v>36686.42989</v>
       </c>
       <c r="F78" t="n">
-        <v>36026.221391</v>
+        <v>36026.209872</v>
       </c>
       <c r="G78" t="n">
-        <v>46103.519515</v>
+        <v>46103.492155</v>
       </c>
       <c r="H78" t="n">
-        <v>61593.915646</v>
+        <v>61593.860154</v>
       </c>
       <c r="I78" t="n">
-        <v>84791.934007</v>
+        <v>84791.82906400001</v>
       </c>
       <c r="J78" t="n">
-        <v>113179.32807</v>
+        <v>113179.144598</v>
       </c>
       <c r="K78" t="n">
-        <v>140760.764627</v>
+        <v>140760.472374</v>
       </c>
       <c r="L78" t="n">
-        <v>167537.637365</v>
+        <v>167537.19724</v>
       </c>
       <c r="M78" t="n">
-        <v>190410.648172</v>
+        <v>190410.017477</v>
       </c>
       <c r="N78" t="n">
-        <v>213038.384115</v>
+        <v>213037.494539</v>
       </c>
       <c r="O78" t="n">
-        <v>247771.160335</v>
+        <v>247769.851972</v>
       </c>
       <c r="P78" t="n">
-        <v>305244.741423</v>
+        <v>305242.694831</v>
       </c>
       <c r="Q78" t="n">
-        <v>339532.380876</v>
+        <v>339529.473627</v>
       </c>
       <c r="R78" t="n">
-        <v>363197.109245</v>
+        <v>363193.105997</v>
       </c>
       <c r="S78" t="n">
-        <v>377327.041577</v>
+        <v>377321.630045</v>
       </c>
       <c r="T78" t="n">
-        <v>391235.675116</v>
+        <v>391228.263411</v>
       </c>
       <c r="U78" t="n">
-        <v>405256.442703</v>
+        <v>405246.074634</v>
       </c>
       <c r="V78" t="n">
-        <v>423367.886256</v>
+        <v>423352.713417</v>
       </c>
     </row>
     <row r="79">
@@ -6378,58 +6378,58 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>41005.449864</v>
+        <v>41005.452166</v>
       </c>
       <c r="F79" t="n">
-        <v>61709.408431</v>
+        <v>61709.41613</v>
       </c>
       <c r="G79" t="n">
-        <v>125273.12755</v>
+        <v>125273.150018</v>
       </c>
       <c r="H79" t="n">
-        <v>233262.058892</v>
+        <v>233262.115103</v>
       </c>
       <c r="I79" t="n">
-        <v>386842.365397</v>
+        <v>386842.487831</v>
       </c>
       <c r="J79" t="n">
-        <v>556081.054434</v>
+        <v>556081.281733</v>
       </c>
       <c r="K79" t="n">
-        <v>698438.239677</v>
+        <v>698438.605234</v>
       </c>
       <c r="L79" t="n">
-        <v>817000.818189</v>
+        <v>817001.364815</v>
       </c>
       <c r="M79" t="n">
-        <v>904890.48699</v>
+        <v>904891.258839</v>
       </c>
       <c r="N79" t="n">
-        <v>986236.342873</v>
+        <v>986237.414287</v>
       </c>
       <c r="O79" t="n">
-        <v>1121677.148193</v>
+        <v>1121678.689798</v>
       </c>
       <c r="P79" t="n">
-        <v>1358199.165018</v>
+        <v>1358201.516621</v>
       </c>
       <c r="Q79" t="n">
-        <v>1491510.385438</v>
+        <v>1491513.637202</v>
       </c>
       <c r="R79" t="n">
-        <v>1579781.912042</v>
+        <v>1579786.270616</v>
       </c>
       <c r="S79" t="n">
-        <v>1627784.336076</v>
+        <v>1627790.087309</v>
       </c>
       <c r="T79" t="n">
-        <v>1675340.058846</v>
+        <v>1675347.779218</v>
       </c>
       <c r="U79" t="n">
-        <v>1724075.345015</v>
+        <v>1724085.974994</v>
       </c>
       <c r="V79" t="n">
-        <v>1792318.947715</v>
+        <v>1792334.297155</v>
       </c>
     </row>
     <row r="80">
@@ -6454,58 +6454,58 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6828.04028</v>
+        <v>6828.040598</v>
       </c>
       <c r="F80" t="n">
-        <v>6761.224151</v>
+        <v>6761.22486</v>
       </c>
       <c r="G80" t="n">
-        <v>9270.609087000001</v>
+        <v>9270.610495000001</v>
       </c>
       <c r="H80" t="n">
-        <v>13787.887308</v>
+        <v>13787.89017</v>
       </c>
       <c r="I80" t="n">
-        <v>21245.711522</v>
+        <v>21245.717331</v>
       </c>
       <c r="J80" t="n">
-        <v>31531.6739</v>
+        <v>31531.684804</v>
       </c>
       <c r="K80" t="n">
-        <v>43230.93237</v>
+        <v>43230.950795</v>
       </c>
       <c r="L80" t="n">
-        <v>55938.906467</v>
+        <v>55938.935657</v>
       </c>
       <c r="M80" t="n">
-        <v>67744.08755700001</v>
+        <v>67744.130897</v>
       </c>
       <c r="N80" t="n">
-        <v>79058.22470399999</v>
+        <v>79058.287243</v>
       </c>
       <c r="O80" t="n">
-        <v>94213.89644</v>
+        <v>94213.98873</v>
       </c>
       <c r="P80" t="n">
-        <v>117399.02704</v>
+        <v>117399.169877</v>
       </c>
       <c r="Q80" t="n">
-        <v>130855.411119</v>
+        <v>130855.609918</v>
       </c>
       <c r="R80" t="n">
-        <v>139295.647757</v>
+        <v>139295.91462</v>
       </c>
       <c r="S80" t="n">
-        <v>143280.277435</v>
+        <v>143280.629428</v>
       </c>
       <c r="T80" t="n">
-        <v>146636.746469</v>
+        <v>146637.218806</v>
       </c>
       <c r="U80" t="n">
-        <v>149704.00304</v>
+        <v>149704.653354</v>
       </c>
       <c r="V80" t="n">
-        <v>154008.009388</v>
+        <v>154008.947418</v>
       </c>
     </row>
     <row r="81">
@@ -6530,58 +6530,58 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>62597.491771</v>
+        <v>62597.49536</v>
       </c>
       <c r="F81" t="n">
-        <v>96312.87633699999</v>
+        <v>96312.888731</v>
       </c>
       <c r="G81" t="n">
-        <v>194536.57028</v>
+        <v>194536.6071</v>
       </c>
       <c r="H81" t="n">
-        <v>359651.414796</v>
+        <v>359651.508365</v>
       </c>
       <c r="I81" t="n">
-        <v>597960.700877</v>
+        <v>597960.90796</v>
       </c>
       <c r="J81" t="n">
-        <v>867589.302721</v>
+        <v>867589.692194</v>
       </c>
       <c r="K81" t="n">
-        <v>1097584.498404</v>
+        <v>1097585.128389</v>
       </c>
       <c r="L81" t="n">
-        <v>1287853.156124</v>
+        <v>1287854.097896</v>
       </c>
       <c r="M81" t="n">
-        <v>1425160.255001</v>
+        <v>1425161.579386</v>
       </c>
       <c r="N81" t="n">
-        <v>1547373.866325</v>
+        <v>1547375.692874</v>
       </c>
       <c r="O81" t="n">
-        <v>1752396.631535</v>
+        <v>1752399.2454</v>
       </c>
       <c r="P81" t="n">
-        <v>2115990.566123</v>
+        <v>2115994.541746</v>
       </c>
       <c r="Q81" t="n">
-        <v>2322590.726232</v>
+        <v>2322596.223938</v>
       </c>
       <c r="R81" t="n">
-        <v>2464411.741516</v>
+        <v>2464419.12972</v>
       </c>
       <c r="S81" t="n">
-        <v>2548937.133318</v>
+        <v>2548946.927357</v>
       </c>
       <c r="T81" t="n">
-        <v>2638565.396214</v>
+        <v>2638578.627118</v>
       </c>
       <c r="U81" t="n">
-        <v>2736892.930916</v>
+        <v>2736911.297091</v>
       </c>
       <c r="V81" t="n">
-        <v>2873079.216039</v>
+        <v>2873105.997988</v>
       </c>
     </row>
     <row r="82">
@@ -6606,58 +6606,58 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>391.581285</v>
+        <v>391.580441</v>
       </c>
       <c r="F82" t="n">
-        <v>449.06344</v>
+        <v>449.060726</v>
       </c>
       <c r="G82" t="n">
-        <v>668.971738</v>
+        <v>668.963737</v>
       </c>
       <c r="H82" t="n">
-        <v>1008.517132</v>
+        <v>1008.49734</v>
       </c>
       <c r="I82" t="n">
-        <v>1492.084685</v>
+        <v>1492.042122</v>
       </c>
       <c r="J82" t="n">
-        <v>2057.756386</v>
+        <v>2057.677097</v>
       </c>
       <c r="K82" t="n">
-        <v>2575.356859</v>
+        <v>2575.228332</v>
       </c>
       <c r="L82" t="n">
-        <v>3051.384245</v>
+        <v>3051.190876</v>
       </c>
       <c r="M82" t="n">
-        <v>3434.394325</v>
+        <v>3434.119983</v>
       </c>
       <c r="N82" t="n">
-        <v>3798.026046</v>
+        <v>3797.644006</v>
       </c>
       <c r="O82" t="n">
-        <v>4366.510956</v>
+        <v>4365.957199</v>
       </c>
       <c r="P82" t="n">
-        <v>5326.125437</v>
+        <v>5325.270955</v>
       </c>
       <c r="Q82" t="n">
-        <v>5876.197297</v>
+        <v>5874.998729</v>
       </c>
       <c r="R82" t="n">
-        <v>6243.923771</v>
+        <v>6242.293108</v>
       </c>
       <c r="S82" t="n">
-        <v>6452.472349</v>
+        <v>6450.293003</v>
       </c>
       <c r="T82" t="n">
-        <v>6668.124071</v>
+        <v>6665.168325</v>
       </c>
       <c r="U82" t="n">
-        <v>6908.126672</v>
+        <v>6904.020847</v>
       </c>
       <c r="V82" t="n">
-        <v>7256.188073</v>
+        <v>7250.21185</v>
       </c>
     </row>
     <row r="83">
@@ -6682,58 +6682,58 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>25308.042482</v>
+        <v>25308.042983</v>
       </c>
       <c r="F83" t="n">
-        <v>39002.703477</v>
+        <v>39002.703377</v>
       </c>
       <c r="G83" t="n">
-        <v>78136.020022</v>
+        <v>78136.00952199999</v>
       </c>
       <c r="H83" t="n">
-        <v>142304.055259</v>
+        <v>142304.005157</v>
       </c>
       <c r="I83" t="n">
-        <v>229882.519767</v>
+        <v>229882.380651</v>
       </c>
       <c r="J83" t="n">
-        <v>322685.634019</v>
+        <v>322685.35829</v>
       </c>
       <c r="K83" t="n">
-        <v>399054.737965</v>
+        <v>399054.298567</v>
       </c>
       <c r="L83" t="n">
-        <v>463708.526362</v>
+        <v>463707.891385</v>
       </c>
       <c r="M83" t="n">
-        <v>513107.735667</v>
+        <v>513106.867004</v>
       </c>
       <c r="N83" t="n">
-        <v>559987.168223</v>
+        <v>559985.9915</v>
       </c>
       <c r="O83" t="n">
-        <v>637767.836767</v>
+        <v>637766.1577550001</v>
       </c>
       <c r="P83" t="n">
-        <v>772732.02641</v>
+        <v>772729.451288</v>
       </c>
       <c r="Q83" t="n">
-        <v>848344.744911</v>
+        <v>848341.129755</v>
       </c>
       <c r="R83" t="n">
-        <v>897629.919982</v>
+        <v>897624.980366</v>
       </c>
       <c r="S83" t="n">
-        <v>923400.720813</v>
+        <v>923394.088287</v>
       </c>
       <c r="T83" t="n">
-        <v>948614.9528570001</v>
+        <v>948605.931466</v>
       </c>
       <c r="U83" t="n">
-        <v>974614.05527</v>
+        <v>974601.516572</v>
       </c>
       <c r="V83" t="n">
-        <v>1011610.514336</v>
+        <v>1011592.288796</v>
       </c>
     </row>
     <row r="84">
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>85661.978021</v>
+        <v>85662.357189</v>
       </c>
       <c r="F86" t="n">
-        <v>104213.315758</v>
+        <v>104214.511327</v>
       </c>
       <c r="G86" t="n">
-        <v>118619.912349</v>
+        <v>118622.682591</v>
       </c>
       <c r="H86" t="n">
-        <v>145838.882727</v>
+        <v>145845.770287</v>
       </c>
       <c r="I86" t="n">
-        <v>184273.924591</v>
+        <v>184295.814895</v>
       </c>
       <c r="J86" t="n">
         <v>175792.788411</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6610.913598</v>
+        <v>6610.676227</v>
       </c>
       <c r="F87" t="n">
-        <v>9004.913790000001</v>
+        <v>9004.080505</v>
       </c>
       <c r="G87" t="n">
-        <v>11626.653906</v>
+        <v>11624.433822</v>
       </c>
       <c r="H87" t="n">
-        <v>15807.613329</v>
+        <v>15801.449485</v>
       </c>
       <c r="I87" t="n">
-        <v>21700.70758</v>
+        <v>21679.4152</v>
       </c>
       <c r="J87" t="n">
         <v>81497.102193</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>183058.037162</v>
+        <v>183057.875376</v>
       </c>
       <c r="F88" t="n">
-        <v>199557.412175</v>
+        <v>199557.237273</v>
       </c>
       <c r="G88" t="n">
-        <v>209053.798836</v>
+        <v>209053.838396</v>
       </c>
       <c r="H88" t="n">
-        <v>249066.566454</v>
+        <v>249067.190983</v>
       </c>
       <c r="I88" t="n">
-        <v>316835.486636</v>
+        <v>316838.160233</v>
       </c>
       <c r="J88" t="n">
         <v>394473.219277</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>39964.608013</v>
+        <v>39965.050319</v>
       </c>
       <c r="F89" t="n">
-        <v>46271.584758</v>
+        <v>46272.915266</v>
       </c>
       <c r="G89" t="n">
-        <v>52460.30695</v>
+        <v>52463.391137</v>
       </c>
       <c r="H89" t="n">
-        <v>64729.212235</v>
+        <v>64736.93831</v>
       </c>
       <c r="I89" t="n">
-        <v>82225.830107</v>
+        <v>82250.597765</v>
       </c>
       <c r="J89" t="n">
         <v>43610.694709</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>129239.961261</v>
+        <v>129240.003454</v>
       </c>
       <c r="F90" t="n">
-        <v>152266.005211</v>
+        <v>152266.21023</v>
       </c>
       <c r="G90" t="n">
-        <v>176478.908495</v>
+        <v>176479.384699</v>
       </c>
       <c r="H90" t="n">
-        <v>223477.386543</v>
+        <v>223478.486867</v>
       </c>
       <c r="I90" t="n">
-        <v>290391.682321</v>
+        <v>290394.914772</v>
       </c>
       <c r="J90" t="n">
         <v>357626.637305</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>60728.064924</v>
+        <v>60728.483044</v>
       </c>
       <c r="F91" t="n">
-        <v>73511.275007</v>
+        <v>73512.58615800001</v>
       </c>
       <c r="G91" t="n">
-        <v>83828.253603</v>
+        <v>83831.300072</v>
       </c>
       <c r="H91" t="n">
-        <v>101316.904089</v>
+        <v>101324.387841</v>
       </c>
       <c r="I91" t="n">
-        <v>123875.355818</v>
+        <v>123898.546326</v>
       </c>
       <c r="J91" t="n">
         <v>93999.896647</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>65782.65955700001</v>
+        <v>65783.497699</v>
       </c>
       <c r="F92" t="n">
-        <v>80358.465712</v>
+        <v>80361.100999</v>
       </c>
       <c r="G92" t="n">
-        <v>94853.439717</v>
+        <v>94859.763727</v>
       </c>
       <c r="H92" t="n">
-        <v>118168.091785</v>
+        <v>118184.043419</v>
       </c>
       <c r="I92" t="n">
-        <v>148083.079912</v>
+        <v>148133.488661</v>
       </c>
       <c r="J92" t="n">
         <v>63356.542468</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>904.5882779999999</v>
+        <v>904.4575160000001</v>
       </c>
       <c r="F93" t="n">
-        <v>1160.416504</v>
+        <v>1159.986956</v>
       </c>
       <c r="G93" t="n">
-        <v>1446.011345</v>
+        <v>1444.913937</v>
       </c>
       <c r="H93" t="n">
-        <v>1957.277183</v>
+        <v>1954.255207</v>
       </c>
       <c r="I93" t="n">
-        <v>2731.57299</v>
+        <v>2721.08597</v>
       </c>
       <c r="J93" t="n">
         <v>29709.772502</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>383962.836065</v>
+        <v>383959.507291</v>
       </c>
       <c r="F94" t="n">
-        <v>494063.467098</v>
+        <v>494052.40805</v>
       </c>
       <c r="G94" t="n">
-        <v>580806.570644</v>
+        <v>580779.933696</v>
       </c>
       <c r="H94" t="n">
-        <v>723016.530725</v>
+        <v>722949.422653</v>
       </c>
       <c r="I94" t="n">
-        <v>915537.218264</v>
+        <v>915324.6342429999</v>
       </c>
       <c r="J94" t="n">
         <v>1618008.0076</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>255644.962661</v>
+        <v>255646.525729</v>
       </c>
       <c r="F95" t="n">
-        <v>334955.47743</v>
+        <v>334960.655265</v>
       </c>
       <c r="G95" t="n">
-        <v>409472.369425</v>
+        <v>409484.959396</v>
       </c>
       <c r="H95" t="n">
-        <v>527501.8312050001</v>
+        <v>527534.09456</v>
       </c>
       <c r="I95" t="n">
-        <v>684440.476077</v>
+        <v>684544.620334</v>
       </c>
       <c r="J95" t="n">
         <v>606667.955844</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>92853.98852499999</v>
+        <v>92854.008458</v>
       </c>
       <c r="F96" t="n">
-        <v>105894.836555</v>
+        <v>105894.993048</v>
       </c>
       <c r="G96" t="n">
-        <v>111665.123961</v>
+        <v>111665.645928</v>
       </c>
       <c r="H96" t="n">
-        <v>131761.548413</v>
+        <v>131763.064682</v>
       </c>
       <c r="I96" t="n">
-        <v>164830.438855</v>
+        <v>164835.615101</v>
       </c>
       <c r="J96" t="n">
         <v>192564.425048</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>46713.871935</v>
+        <v>46714.027699</v>
       </c>
       <c r="F97" t="n">
-        <v>49187.038539</v>
+        <v>49187.523459</v>
       </c>
       <c r="G97" t="n">
-        <v>50349.181431</v>
+        <v>50350.283262</v>
       </c>
       <c r="H97" t="n">
-        <v>59236.04864</v>
+        <v>59238.789034</v>
       </c>
       <c r="I97" t="n">
-        <v>74990.79592400001</v>
+        <v>74999.675575</v>
       </c>
       <c r="J97" t="n">
         <v>73446.420747</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>426924.359937</v>
+        <v>426932.261951</v>
       </c>
       <c r="F98" t="n">
-        <v>471835.634646</v>
+        <v>471858.487613</v>
       </c>
       <c r="G98" t="n">
-        <v>532691.3483749999</v>
+        <v>532745.769749</v>
       </c>
       <c r="H98" t="n">
-        <v>585800.289585</v>
+        <v>585925.726399</v>
       </c>
       <c r="I98" t="n">
-        <v>678021.409053</v>
+        <v>678398.060369</v>
       </c>
       <c r="J98" t="n">
         <v>335834.504952</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>160742.92318</v>
+        <v>160739.924185</v>
       </c>
       <c r="F99" t="n">
-        <v>204932.01848</v>
+        <v>204922.202908</v>
       </c>
       <c r="G99" t="n">
-        <v>271028.698285</v>
+        <v>271002.060676</v>
       </c>
       <c r="H99" t="n">
-        <v>337376.074365</v>
+        <v>337308.614214</v>
       </c>
       <c r="I99" t="n">
-        <v>426464.354829</v>
+        <v>426249.572891</v>
       </c>
       <c r="J99" t="n">
         <v>830574.560561</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>207478.851544</v>
+        <v>207482.142768</v>
       </c>
       <c r="F100" t="n">
-        <v>227065.807304</v>
+        <v>227075.325686</v>
       </c>
       <c r="G100" t="n">
-        <v>260402.015646</v>
+        <v>260425.185247</v>
       </c>
       <c r="H100" t="n">
-        <v>292515.169149</v>
+        <v>292569.946824</v>
       </c>
       <c r="I100" t="n">
-        <v>345743.557515</v>
+        <v>345911.968413</v>
       </c>
       <c r="J100" t="n">
         <v>204867.432629</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>457383.928785</v>
+        <v>457395.742047</v>
       </c>
       <c r="F101" t="n">
-        <v>537743.395194</v>
+        <v>537779.212584</v>
       </c>
       <c r="G101" t="n">
-        <v>653998.3415400001</v>
+        <v>654088.707236</v>
       </c>
       <c r="H101" t="n">
-        <v>761922.359319</v>
+        <v>762140.142481</v>
       </c>
       <c r="I101" t="n">
-        <v>916698.118978</v>
+        <v>917371.769443</v>
       </c>
       <c r="J101" t="n">
         <v>253422.100659</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>999147.907552</v>
+        <v>999139.613062</v>
       </c>
       <c r="F102" t="n">
-        <v>1245872.892132</v>
+        <v>1245846.958218</v>
       </c>
       <c r="G102" t="n">
-        <v>1624646.019778</v>
+        <v>1624578.073798</v>
       </c>
       <c r="H102" t="n">
-        <v>2016198.514594</v>
+        <v>2016029.693541</v>
       </c>
       <c r="I102" t="n">
-        <v>2561062.422567</v>
+        <v>2560528.197082</v>
       </c>
       <c r="J102" t="n">
         <v>4020343.479512</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1701883.154845</v>
+        <v>1701888.801018</v>
       </c>
       <c r="F103" t="n">
-        <v>1813178.845806</v>
+        <v>1813197.999471</v>
       </c>
       <c r="G103" t="n">
-        <v>1994167.900712</v>
+        <v>1994220.469421</v>
       </c>
       <c r="H103" t="n">
-        <v>2154926.676522</v>
+        <v>2155059.722093</v>
       </c>
       <c r="I103" t="n">
-        <v>2470005.997029</v>
+        <v>2470429.714334</v>
       </c>
       <c r="J103" t="n">
         <v>2406090.810116</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>123648.933628</v>
+        <v>123646.483572</v>
       </c>
       <c r="F104" t="n">
-        <v>148540.322717</v>
+        <v>148532.886117</v>
       </c>
       <c r="G104" t="n">
-        <v>186064.845789</v>
+        <v>186045.989632</v>
       </c>
       <c r="H104" t="n">
-        <v>225886.701781</v>
+        <v>225840.149924</v>
       </c>
       <c r="I104" t="n">
-        <v>283409.738273</v>
+        <v>283261.632925</v>
       </c>
       <c r="J104" t="n">
         <v>561667.873027</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>48831.194584</v>
+        <v>48829.519916</v>
       </c>
       <c r="F105" t="n">
-        <v>59168.651245</v>
+        <v>59163.584849</v>
       </c>
       <c r="G105" t="n">
-        <v>75581.627437</v>
+        <v>75568.596739</v>
       </c>
       <c r="H105" t="n">
-        <v>92114.27592</v>
+        <v>92082.34141399999</v>
       </c>
       <c r="I105" t="n">
-        <v>115218.211694</v>
+        <v>115118.365452</v>
       </c>
       <c r="J105" t="n">
         <v>277662.498141</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1145567.141794</v>
+        <v>1145570.676034</v>
       </c>
       <c r="F106" t="n">
-        <v>1437500.130344</v>
+        <v>1437511.436078</v>
       </c>
       <c r="G106" t="n">
-        <v>1904077.299782</v>
+        <v>1904107.618124</v>
       </c>
       <c r="H106" t="n">
-        <v>2373373.95728</v>
+        <v>2373451.951185</v>
       </c>
       <c r="I106" t="n">
-        <v>2993704.970037</v>
+        <v>2993961.545059</v>
       </c>
       <c r="J106" t="n">
         <v>3455513.121635</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>9020.259316</v>
+        <v>9019.274676999999</v>
       </c>
       <c r="F107" t="n">
-        <v>11941.560525</v>
+        <v>11938.221539</v>
       </c>
       <c r="G107" t="n">
-        <v>15552.52275</v>
+        <v>15543.698074</v>
       </c>
       <c r="H107" t="n">
-        <v>19166.431393</v>
+        <v>19144.465181</v>
       </c>
       <c r="I107" t="n">
-        <v>24462.567443</v>
+        <v>24392.278041</v>
       </c>
       <c r="J107" t="n">
         <v>127603.921903</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>156708.929485</v>
+        <v>156698.949064</v>
       </c>
       <c r="F108" t="n">
-        <v>187292.704335</v>
+        <v>187262.563484</v>
       </c>
       <c r="G108" t="n">
-        <v>228784.271474</v>
+        <v>228710.051443</v>
       </c>
       <c r="H108" t="n">
-        <v>267757.524117</v>
+        <v>267582.734201</v>
       </c>
       <c r="I108" t="n">
-        <v>324596.515119</v>
+        <v>324066.054947</v>
       </c>
       <c r="J108" t="n">
         <v>1089689.603313</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>216538.247032</v>
+        <v>216541.416429</v>
       </c>
       <c r="F109" t="n">
-        <v>261332.80012</v>
+        <v>261342.710779</v>
       </c>
       <c r="G109" t="n">
-        <v>343546.746216</v>
+        <v>343573.650575</v>
       </c>
       <c r="H109" t="n">
-        <v>440871.066863</v>
+        <v>440941.808351</v>
       </c>
       <c r="I109" t="n">
-        <v>583907.2064340001</v>
+        <v>584145.307947</v>
       </c>
       <c r="J109" t="n">
         <v>447625.160505</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>830369.5661310001</v>
+        <v>830390.149846</v>
       </c>
       <c r="F110" t="n">
-        <v>1053089.305071</v>
+        <v>1053156.435052</v>
       </c>
       <c r="G110" t="n">
-        <v>1391908.205041</v>
+        <v>1392091.703796</v>
       </c>
       <c r="H110" t="n">
-        <v>1730681.232818</v>
+        <v>1731152.235138</v>
       </c>
       <c r="I110" t="n">
-        <v>2180086.679716</v>
+        <v>2181610.38712</v>
       </c>
       <c r="J110" t="n">
         <v>728827.741511</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>723995.280533</v>
+        <v>723991.734041</v>
       </c>
       <c r="F111" t="n">
-        <v>895796.9389759999</v>
+        <v>895786.059118</v>
       </c>
       <c r="G111" t="n">
-        <v>1143396.242406</v>
+        <v>1143369.133047</v>
       </c>
       <c r="H111" t="n">
-        <v>1386241.857705</v>
+        <v>1386178.266048</v>
       </c>
       <c r="I111" t="n">
-        <v>1728716.627155</v>
+        <v>1728525.113951</v>
       </c>
       <c r="J111" t="n">
         <v>2447551.980286</v>
@@ -8858,7 +8858,7 @@
         <v>3420711.246781</v>
       </c>
       <c r="U111" t="n">
-        <v>3329696.692258</v>
+        <v>3329696.692259</v>
       </c>
       <c r="V111" t="n">
         <v>3217725.546782</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>597039.821655</v>
+        <v>597013.811389</v>
       </c>
       <c r="F112" t="n">
-        <v>748225.813407</v>
+        <v>748142.736807</v>
       </c>
       <c r="G112" t="n">
-        <v>986642.438519</v>
+        <v>986417.816194</v>
       </c>
       <c r="H112" t="n">
-        <v>1237088.459196</v>
+        <v>1236512.793613</v>
       </c>
       <c r="I112" t="n">
-        <v>1585927.858375</v>
+        <v>1584056.266244</v>
       </c>
       <c r="J112" t="n">
         <v>4606484.689215</v>
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>57867.014551</v>
+        <v>57866.917047</v>
       </c>
       <c r="F113" t="n">
-        <v>52053.775447</v>
+        <v>52053.542089</v>
       </c>
       <c r="G113" t="n">
-        <v>63253.643416</v>
+        <v>63253.128734</v>
       </c>
       <c r="H113" t="n">
-        <v>89940.588152</v>
+        <v>89939.326632</v>
       </c>
       <c r="I113" t="n">
-        <v>123134.738409</v>
+        <v>123131.029583</v>
       </c>
       <c r="J113" t="n">
         <v>173520.836648</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>28461.591882</v>
+        <v>28461.803051</v>
       </c>
       <c r="F114" t="n">
-        <v>36651.705408</v>
+        <v>36652.423602</v>
       </c>
       <c r="G114" t="n">
-        <v>67678.278907</v>
+        <v>67681.036842</v>
       </c>
       <c r="H114" t="n">
-        <v>127796.199996</v>
+        <v>127806.949324</v>
       </c>
       <c r="I114" t="n">
-        <v>201813.827478</v>
+        <v>201857.38291</v>
       </c>
       <c r="J114" t="n">
         <v>50685.598572</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>114008.559567</v>
+        <v>114008.445902</v>
       </c>
       <c r="F115" t="n">
-        <v>118549.394004</v>
+        <v>118548.909168</v>
       </c>
       <c r="G115" t="n">
-        <v>181957.032599</v>
+        <v>181954.789345</v>
       </c>
       <c r="H115" t="n">
-        <v>308517.389816</v>
+        <v>308507.902008</v>
       </c>
       <c r="I115" t="n">
-        <v>469037.4092</v>
+        <v>468997.562593</v>
       </c>
       <c r="J115" t="n">
         <v>833767.338937</v>
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>25216.446836</v>
+        <v>25216.482245</v>
       </c>
       <c r="F116" t="n">
-        <v>26905.801907</v>
+        <v>26905.900018</v>
       </c>
       <c r="G116" t="n">
-        <v>34484.18539</v>
+        <v>34484.447784</v>
       </c>
       <c r="H116" t="n">
-        <v>44396.577133</v>
+        <v>44397.278689</v>
       </c>
       <c r="I116" t="n">
-        <v>58335.63924</v>
+        <v>58338.016568</v>
       </c>
       <c r="J116" t="n">
         <v>20297.006444</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>34799.864728</v>
+        <v>34799.884205</v>
       </c>
       <c r="F117" t="n">
-        <v>44266.565046</v>
+        <v>44266.621929</v>
       </c>
       <c r="G117" t="n">
-        <v>60167.109101</v>
+        <v>60167.263112</v>
       </c>
       <c r="H117" t="n">
-        <v>78877.961284</v>
+        <v>78878.37396899999</v>
       </c>
       <c r="I117" t="n">
-        <v>103677.28731</v>
+        <v>103678.681499</v>
       </c>
       <c r="J117" t="n">
         <v>101256.899459</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>65563.57434599999</v>
+        <v>65563.588431</v>
       </c>
       <c r="F118" t="n">
-        <v>65859.72128100001</v>
+        <v>65859.761252</v>
       </c>
       <c r="G118" t="n">
-        <v>78869.250932</v>
+        <v>78869.362155</v>
       </c>
       <c r="H118" t="n">
-        <v>96129.953572</v>
+        <v>96130.25962700001</v>
       </c>
       <c r="I118" t="n">
-        <v>121368.167546</v>
+        <v>121369.224033</v>
       </c>
       <c r="J118" t="n">
         <v>127878.470062</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>13864.257626</v>
+        <v>13864.259473</v>
       </c>
       <c r="F119" t="n">
-        <v>16866.687467</v>
+        <v>16866.690888</v>
       </c>
       <c r="G119" t="n">
-        <v>24070.85885</v>
+        <v>24070.863849</v>
       </c>
       <c r="H119" t="n">
-        <v>33610.836089</v>
+        <v>33610.840802</v>
       </c>
       <c r="I119" t="n">
-        <v>46816.541955</v>
+        <v>46816.539266</v>
       </c>
       <c r="J119" t="n">
         <v>63673.987955</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>9960.062744999999</v>
+        <v>9960.072662</v>
       </c>
       <c r="F120" t="n">
-        <v>10716.568127</v>
+        <v>10716.595829</v>
       </c>
       <c r="G120" t="n">
-        <v>13879.083083</v>
+        <v>13879.158027</v>
       </c>
       <c r="H120" t="n">
-        <v>18091.730581</v>
+        <v>18091.933713</v>
       </c>
       <c r="I120" t="n">
-        <v>24111.25793</v>
+        <v>24111.956766</v>
       </c>
       <c r="J120" t="n">
         <v>15237.734568</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>64609.498788</v>
+        <v>64609.491529</v>
       </c>
       <c r="F121" t="n">
-        <v>77695.799042</v>
+        <v>77695.76282800001</v>
       </c>
       <c r="G121" t="n">
-        <v>109693.983268</v>
+        <v>109693.847903</v>
       </c>
       <c r="H121" t="n">
-        <v>149866.118159</v>
+        <v>149865.691354</v>
       </c>
       <c r="I121" t="n">
-        <v>202025.149309</v>
+        <v>202023.629816</v>
       </c>
       <c r="J121" t="n">
         <v>297921.103122</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>523760.58493</v>
+        <v>523760.511456</v>
       </c>
       <c r="F122" t="n">
-        <v>566050.818729</v>
+        <v>566050.628855</v>
       </c>
       <c r="G122" t="n">
-        <v>738698.78812</v>
+        <v>738698.315914</v>
       </c>
       <c r="H122" t="n">
-        <v>972792.634523</v>
+        <v>972791.433189</v>
       </c>
       <c r="I122" t="n">
-        <v>1313036.171603</v>
+        <v>1313032.166945</v>
       </c>
       <c r="J122" t="n">
         <v>1849644.261194</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185876.565468</v>
+        <v>185928.60939</v>
       </c>
       <c r="F123" t="n">
-        <v>232574.992676</v>
+        <v>232729.637826</v>
       </c>
       <c r="G123" t="n">
-        <v>264368.9414</v>
+        <v>264699.954284</v>
       </c>
       <c r="H123" t="n">
-        <v>297096.106562</v>
+        <v>297800.122878</v>
       </c>
       <c r="I123" t="n">
-        <v>354115.032041</v>
+        <v>356093.575502</v>
       </c>
       <c r="J123" t="n">
         <v>53256.567285</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>500125.537526</v>
+        <v>500163.667586</v>
       </c>
       <c r="F124" t="n">
-        <v>620036.422446</v>
+        <v>620141.863655</v>
       </c>
       <c r="G124" t="n">
-        <v>689527.315876</v>
+        <v>689729.917001</v>
       </c>
       <c r="H124" t="n">
-        <v>758318.310141</v>
+        <v>758705.769066</v>
       </c>
       <c r="I124" t="n">
-        <v>887751.749614</v>
+        <v>888729.725909</v>
       </c>
       <c r="J124" t="n">
         <v>892314.999342</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>197261.203006</v>
+        <v>197171.029024</v>
       </c>
       <c r="F125" t="n">
-        <v>226395.348848</v>
+        <v>226135.262488</v>
       </c>
       <c r="G125" t="n">
-        <v>231486.21695</v>
+        <v>230952.602941</v>
       </c>
       <c r="H125" t="n">
-        <v>240850.036735</v>
+        <v>239758.561494</v>
       </c>
       <c r="I125" t="n">
-        <v>278756.428475</v>
+        <v>275799.908719</v>
       </c>
       <c r="J125" t="n">
         <v>880739.73843</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4885.210558</v>
+        <v>4885.170499</v>
       </c>
       <c r="F130" t="n">
-        <v>27013.298015</v>
+        <v>27012.59398</v>
       </c>
       <c r="G130" t="n">
-        <v>54249.144698</v>
+        <v>54245.365894</v>
       </c>
       <c r="H130" t="n">
-        <v>97609.621077</v>
+        <v>97590.43575800001</v>
       </c>
       <c r="I130" t="n">
-        <v>180555.875336</v>
+        <v>180417.735886</v>
       </c>
       <c r="J130" t="n">
         <v>5637463.859209</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.001832</v>
+        <v>0.000389</v>
       </c>
       <c r="F131" t="n">
-        <v>0.039664</v>
+        <v>0.008432</v>
       </c>
       <c r="G131" t="n">
-        <v>0.201326</v>
+        <v>0.042802</v>
       </c>
       <c r="H131" t="n">
-        <v>0.922679</v>
+        <v>0.196161</v>
       </c>
       <c r="I131" t="n">
-        <v>6.133061</v>
+        <v>1.303929</v>
       </c>
       <c r="J131" t="n">
         <v>180122.071228</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>80794.564037</v>
+        <v>80794.601551</v>
       </c>
       <c r="F132" t="n">
-        <v>405524.960764</v>
+        <v>405525.497785</v>
       </c>
       <c r="G132" t="n">
-        <v>716082.7660140001</v>
+        <v>716085.126504</v>
       </c>
       <c r="H132" t="n">
-        <v>1135769.623361</v>
+        <v>1135780.097428</v>
       </c>
       <c r="I132" t="n">
-        <v>1920780.890825</v>
+        <v>1920850.678726</v>
       </c>
       <c r="J132" t="n">
         <v>542734.545031</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>12208.878488</v>
+        <v>12208.884589</v>
       </c>
       <c r="F133" t="n">
-        <v>92939.70057</v>
+        <v>92939.819414</v>
       </c>
       <c r="G133" t="n">
-        <v>237600.48786</v>
+        <v>237601.118024</v>
       </c>
       <c r="H133" t="n">
-        <v>479372.716743</v>
+        <v>479375.796819</v>
       </c>
       <c r="I133" t="n">
-        <v>907823.9753620001</v>
+        <v>907846.0968300001</v>
       </c>
       <c r="J133" t="n">
         <v>661164.234445</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>23317.148943</v>
+        <v>23317.156848</v>
       </c>
       <c r="F134" t="n">
-        <v>108399.781164</v>
+        <v>108399.897428</v>
       </c>
       <c r="G134" t="n">
-        <v>184521.406874</v>
+        <v>184521.938767</v>
       </c>
       <c r="H134" t="n">
-        <v>294000.330273</v>
+        <v>294002.809978</v>
       </c>
       <c r="I134" t="n">
-        <v>506417.801913</v>
+        <v>506435.075788</v>
       </c>
       <c r="J134" t="n">
         <v>174336.125992</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>8072.122847</v>
+        <v>8072.127338</v>
       </c>
       <c r="F135" t="n">
-        <v>51330.878204</v>
+        <v>51330.960018</v>
       </c>
       <c r="G135" t="n">
-        <v>116636.154864</v>
+        <v>116636.610456</v>
       </c>
       <c r="H135" t="n">
-        <v>226025.23937</v>
+        <v>226027.65163</v>
       </c>
       <c r="I135" t="n">
-        <v>436862.265513</v>
+        <v>436880.369909</v>
       </c>
       <c r="J135" t="n">
         <v>44988.442155</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1325.405565</v>
+        <v>1325.397424</v>
       </c>
       <c r="F136" t="n">
-        <v>6219.466427</v>
+        <v>6219.372183</v>
       </c>
       <c r="G136" t="n">
-        <v>9816.898306999999</v>
+        <v>9816.631459</v>
       </c>
       <c r="H136" t="n">
-        <v>14054.566519</v>
+        <v>14053.848743</v>
       </c>
       <c r="I136" t="n">
-        <v>22433.946657</v>
+        <v>22430.600452</v>
       </c>
       <c r="J136" t="n">
         <v>137598.871044</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>10012.479144</v>
+        <v>10012.483935</v>
       </c>
       <c r="F137" t="n">
-        <v>51694.950177</v>
+        <v>51695.019951</v>
       </c>
       <c r="G137" t="n">
-        <v>90685.581464</v>
+        <v>90685.88602799999</v>
       </c>
       <c r="H137" t="n">
-        <v>142886.265216</v>
+        <v>142887.606805</v>
       </c>
       <c r="I137" t="n">
-        <v>238545.483804</v>
+        <v>238554.318437</v>
       </c>
       <c r="J137" t="n">
         <v>57960.678698</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>116.75961</v>
+        <v>116.758158</v>
       </c>
       <c r="F138" t="n">
-        <v>583.6988260000001</v>
+        <v>583.677667</v>
       </c>
       <c r="G138" t="n">
-        <v>1035.80455</v>
+        <v>1035.717617</v>
       </c>
       <c r="H138" t="n">
-        <v>1626.094978</v>
+        <v>1625.770316</v>
       </c>
       <c r="I138" t="n">
-        <v>2648.413408</v>
+        <v>2646.662836</v>
       </c>
       <c r="J138" t="n">
         <v>57352.842871</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>373.763635</v>
+        <v>373.763611</v>
       </c>
       <c r="F139" t="n">
-        <v>2026.237464</v>
+        <v>2026.236746</v>
       </c>
       <c r="G139" t="n">
-        <v>4022.971465</v>
+        <v>4022.966451</v>
       </c>
       <c r="H139" t="n">
-        <v>7191.185273</v>
+        <v>7191.158029</v>
       </c>
       <c r="I139" t="n">
-        <v>13236.87708</v>
+        <v>13236.681842</v>
       </c>
       <c r="J139" t="n">
         <v>29840.358202</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>518.8215279999999</v>
+        <v>518.807762</v>
       </c>
       <c r="F140" t="n">
-        <v>2418.571014</v>
+        <v>2418.410333</v>
       </c>
       <c r="G140" t="n">
-        <v>4132.484267</v>
+        <v>4131.904941</v>
       </c>
       <c r="H140" t="n">
-        <v>6623.115889</v>
+        <v>6620.909584</v>
       </c>
       <c r="I140" t="n">
-        <v>11511.811838</v>
+        <v>11498.240281</v>
       </c>
       <c r="J140" t="n">
         <v>511751.048331</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1965.077288</v>
+        <v>1965.078171</v>
       </c>
       <c r="F141" t="n">
-        <v>11208.289396</v>
+        <v>11208.303051</v>
       </c>
       <c r="G141" t="n">
-        <v>22895.462225</v>
+        <v>22895.527339</v>
       </c>
       <c r="H141" t="n">
-        <v>41125.101881</v>
+        <v>41125.414097</v>
       </c>
       <c r="I141" t="n">
-        <v>75988.786861</v>
+        <v>75990.992041</v>
       </c>
       <c r="J141" t="n">
         <v>46581.686289</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5828.237725</v>
+        <v>5828.240924</v>
       </c>
       <c r="F142" t="n">
-        <v>49196.331301</v>
+        <v>49196.405996</v>
       </c>
       <c r="G142" t="n">
-        <v>155728.666646</v>
+        <v>155729.194277</v>
       </c>
       <c r="H142" t="n">
-        <v>379026.076052</v>
+        <v>379029.163962</v>
       </c>
       <c r="I142" t="n">
-        <v>822728.5749520001</v>
+        <v>822752.079652</v>
       </c>
       <c r="J142" t="n">
         <v>551469.4866140001</v>
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>7288.876115</v>
+        <v>7288.892685</v>
       </c>
       <c r="F146" t="n">
-        <v>7341.876568</v>
+        <v>7341.924274</v>
       </c>
       <c r="G146" t="n">
-        <v>8050.069361</v>
+        <v>8050.187784</v>
       </c>
       <c r="H146" t="n">
-        <v>9944.063026</v>
+        <v>9944.380179</v>
       </c>
       <c r="I146" t="n">
-        <v>13302.7698</v>
+        <v>13303.875374</v>
       </c>
       <c r="J146" t="n">
         <v>5635.402429</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3036.569041</v>
+        <v>3036.553598</v>
       </c>
       <c r="F147" t="n">
-        <v>3465.688535</v>
+        <v>3465.640955</v>
       </c>
       <c r="G147" t="n">
-        <v>4094.773208</v>
+        <v>4094.65457</v>
       </c>
       <c r="H147" t="n">
-        <v>5087.098599</v>
+        <v>5086.791474</v>
       </c>
       <c r="I147" t="n">
-        <v>6681.95456</v>
+        <v>6680.895792</v>
       </c>
       <c r="J147" t="n">
         <v>21227.203916</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>303583.881788</v>
+        <v>303583.88066</v>
       </c>
       <c r="F148" t="n">
-        <v>368151.381353</v>
+        <v>368151.381227</v>
       </c>
       <c r="G148" t="n">
-        <v>474358.94007</v>
+        <v>474358.940284</v>
       </c>
       <c r="H148" t="n">
-        <v>629595.89355</v>
+        <v>629595.883522</v>
       </c>
       <c r="I148" t="n">
-        <v>840753.295536</v>
+        <v>840753.24873</v>
       </c>
       <c r="J148" t="n">
         <v>1138455.766117</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>48874.508341</v>
+        <v>48874.48277</v>
       </c>
       <c r="F149" t="n">
-        <v>56760.56699</v>
+        <v>56760.494723</v>
       </c>
       <c r="G149" t="n">
-        <v>69251.41351499999</v>
+        <v>69251.23491299999</v>
       </c>
       <c r="H149" t="n">
-        <v>89795.61668200001</v>
+        <v>89795.137004</v>
       </c>
       <c r="I149" t="n">
-        <v>125068.383943</v>
+        <v>125066.650433</v>
       </c>
       <c r="J149" t="n">
         <v>254391.68365</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>395457.789513</v>
+        <v>395457.819885</v>
       </c>
       <c r="F150" t="n">
-        <v>447051.799434</v>
+        <v>447051.901104</v>
       </c>
       <c r="G150" t="n">
-        <v>532612.356103</v>
+        <v>532612.580537</v>
       </c>
       <c r="H150" t="n">
-        <v>660290.813193</v>
+        <v>660291.242625</v>
       </c>
       <c r="I150" t="n">
-        <v>851245.770946</v>
+        <v>851246.62142</v>
       </c>
       <c r="J150" t="n">
         <v>1054052.31195</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>68684.788203</v>
+        <v>68684.653785</v>
       </c>
       <c r="F151" t="n">
-        <v>83953.05405399999</v>
+        <v>83952.64605</v>
       </c>
       <c r="G151" t="n">
-        <v>107066.18451</v>
+        <v>107065.140919</v>
       </c>
       <c r="H151" t="n">
-        <v>139348.638591</v>
+        <v>139345.905816</v>
       </c>
       <c r="I151" t="n">
-        <v>186532.155745</v>
+        <v>186523.036886</v>
       </c>
       <c r="J151" t="n">
         <v>637399.975563</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>232316.651666</v>
+        <v>232316.393674</v>
       </c>
       <c r="F152" t="n">
-        <v>285789.402708</v>
+        <v>285788.617894</v>
       </c>
       <c r="G152" t="n">
-        <v>347309.293894</v>
+        <v>347307.375539</v>
       </c>
       <c r="H152" t="n">
-        <v>427668.627706</v>
+        <v>427663.837285</v>
       </c>
       <c r="I152" t="n">
-        <v>545335.2353619999</v>
+        <v>545319.824101</v>
       </c>
       <c r="J152" t="n">
         <v>1310825.676605</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>294553.583806</v>
+        <v>294553.909486</v>
       </c>
       <c r="F153" t="n">
-        <v>347004.834731</v>
+        <v>347005.806766</v>
       </c>
       <c r="G153" t="n">
-        <v>442475.688188</v>
+        <v>442478.153128</v>
       </c>
       <c r="H153" t="n">
-        <v>596936.99472</v>
+        <v>596943.527391</v>
       </c>
       <c r="I153" t="n">
-        <v>841254.101088</v>
+        <v>841276.4995180001</v>
       </c>
       <c r="J153" t="n">
         <v>176791.106399</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>119981.434471</v>
+        <v>119981.4964</v>
       </c>
       <c r="F154" t="n">
-        <v>144516.363044</v>
+        <v>144516.554426</v>
       </c>
       <c r="G154" t="n">
-        <v>172602.635403</v>
+        <v>172603.086578</v>
       </c>
       <c r="H154" t="n">
-        <v>206870.375638</v>
+        <v>206871.416409</v>
       </c>
       <c r="I154" t="n">
-        <v>253607.906602</v>
+        <v>253610.921328</v>
       </c>
       <c r="J154" t="n">
         <v>191174.468909</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>190009.256529</v>
+        <v>189966.567851</v>
       </c>
       <c r="F155" t="n">
-        <v>185833.844588</v>
+        <v>185735.169543</v>
       </c>
       <c r="G155" t="n">
-        <v>225393.995265</v>
+        <v>225170.814935</v>
       </c>
       <c r="H155" t="n">
-        <v>301212.547441</v>
+        <v>300674.009088</v>
       </c>
       <c r="I155" t="n">
-        <v>435257.338049</v>
+        <v>433606.242801</v>
       </c>
       <c r="J155" t="n">
         <v>400865.745443</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>373449.793301</v>
+        <v>373654.237957</v>
       </c>
       <c r="F156" t="n">
-        <v>355342.606156</v>
+        <v>355795.412522</v>
       </c>
       <c r="G156" t="n">
-        <v>419101.33977</v>
+        <v>420098.079732</v>
       </c>
       <c r="H156" t="n">
-        <v>544008.44955</v>
+        <v>546404.860615</v>
       </c>
       <c r="I156" t="n">
-        <v>775102.954451</v>
+        <v>782626.5897979999</v>
       </c>
       <c r="J156" t="n">
         <v>2089000.676566</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4273.545055</v>
+        <v>4276.455366</v>
       </c>
       <c r="F157" t="n">
-        <v>5004.263942</v>
+        <v>5011.461534</v>
       </c>
       <c r="G157" t="n">
-        <v>6647.807838</v>
+        <v>6664.758871</v>
       </c>
       <c r="H157" t="n">
-        <v>8895.311314</v>
+        <v>8937.279262</v>
       </c>
       <c r="I157" t="n">
-        <v>12469.350592</v>
+        <v>12602.148409</v>
       </c>
       <c r="J157" t="n">
         <v>34758.974681</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>207015.739204</v>
+        <v>207013.920744</v>
       </c>
       <c r="F158" t="n">
-        <v>167959.237313</v>
+        <v>167962.981144</v>
       </c>
       <c r="G158" t="n">
-        <v>168524.649434</v>
+        <v>168548.451836</v>
       </c>
       <c r="H158" t="n">
-        <v>192997.494397</v>
+        <v>193083.187451</v>
       </c>
       <c r="I158" t="n">
-        <v>250386.453861</v>
+        <v>250728.320652</v>
       </c>
       <c r="J158" t="n">
         <v>380676.365216</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1819.820759</v>
+        <v>1820.795055</v>
       </c>
       <c r="F159" t="n">
-        <v>1625.182833</v>
+        <v>1627.305706</v>
       </c>
       <c r="G159" t="n">
-        <v>1819.206401</v>
+        <v>1823.815512</v>
       </c>
       <c r="H159" t="n">
-        <v>2244.190664</v>
+        <v>2255.09469</v>
       </c>
       <c r="I159" t="n">
-        <v>3062.011031</v>
+        <v>3095.680698</v>
       </c>
       <c r="J159" t="n">
         <v>8518.20816</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>434806.033152</v>
+        <v>434642.211026</v>
       </c>
       <c r="F160" t="n">
-        <v>410376.45062</v>
+        <v>410009.255003</v>
       </c>
       <c r="G160" t="n">
-        <v>485214.439531</v>
+        <v>484395.517353</v>
       </c>
       <c r="H160" t="n">
-        <v>640832.121956</v>
+        <v>638835.684215</v>
       </c>
       <c r="I160" t="n">
-        <v>927050.758115</v>
+        <v>920669.88374</v>
       </c>
       <c r="J160" t="n">
         <v>444938.916712</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>15.267643</v>
+        <v>14.730793</v>
       </c>
       <c r="F162" t="n">
-        <v>19.103408</v>
+        <v>18.195302</v>
       </c>
       <c r="G162" t="n">
-        <v>29.629431</v>
+        <v>28.032881</v>
       </c>
       <c r="H162" t="n">
-        <v>57.741639</v>
+        <v>54.408411</v>
       </c>
       <c r="I162" t="n">
-        <v>164.793652</v>
+        <v>154.888828</v>
       </c>
       <c r="J162" t="n">
         <v>23182.143984</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4209.577014</v>
+        <v>4209.537805</v>
       </c>
       <c r="F163" t="n">
-        <v>4720.703557</v>
+        <v>4720.584503</v>
       </c>
       <c r="G163" t="n">
-        <v>6852.355119</v>
+        <v>6851.984165</v>
       </c>
       <c r="H163" t="n">
-        <v>10034.290217</v>
+        <v>10033.14644</v>
       </c>
       <c r="I163" t="n">
-        <v>14495.337612</v>
+        <v>14491.087522</v>
       </c>
       <c r="J163" t="n">
         <v>30301.496564</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>129316.757957</v>
+        <v>129318.623315</v>
       </c>
       <c r="F164" t="n">
-        <v>163442.821735</v>
+        <v>163448.477993</v>
       </c>
       <c r="G164" t="n">
-        <v>257297.157337</v>
+        <v>257314.306183</v>
       </c>
       <c r="H164" t="n">
-        <v>406453.952358</v>
+        <v>406506.342084</v>
       </c>
       <c r="I164" t="n">
-        <v>631653.2560779999</v>
+        <v>631850.257305</v>
       </c>
       <c r="J164" t="n">
         <v>396983.064378</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>109753.675933</v>
+        <v>109755.488999</v>
       </c>
       <c r="F165" t="n">
-        <v>122512.810023</v>
+        <v>122517.711402</v>
       </c>
       <c r="G165" t="n">
-        <v>154160.836746</v>
+        <v>154172.848184</v>
       </c>
       <c r="H165" t="n">
-        <v>205107.820445</v>
+        <v>205139.029389</v>
       </c>
       <c r="I165" t="n">
-        <v>284320.271956</v>
+        <v>284425.82163</v>
       </c>
       <c r="J165" t="n">
         <v>124220.788637</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>468670.823837</v>
+        <v>468679.412557</v>
       </c>
       <c r="F166" t="n">
-        <v>484210.638549</v>
+        <v>484232.224397</v>
       </c>
       <c r="G166" t="n">
-        <v>623246.714249</v>
+        <v>623300.964181</v>
       </c>
       <c r="H166" t="n">
-        <v>843729.429369</v>
+        <v>843873.188443</v>
       </c>
       <c r="I166" t="n">
-        <v>1160296.228285</v>
+        <v>1160779.820264</v>
       </c>
       <c r="J166" t="n">
         <v>362952.440338</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>75623.373463</v>
+        <v>75613.18113500001</v>
       </c>
       <c r="F167" t="n">
-        <v>74433.922148</v>
+        <v>74408.767922</v>
       </c>
       <c r="G167" t="n">
-        <v>93297.583423</v>
+        <v>93234.502937</v>
       </c>
       <c r="H167" t="n">
-        <v>128158.443517</v>
+        <v>127986.263496</v>
       </c>
       <c r="I167" t="n">
-        <v>187855.090009</v>
+        <v>187245.581614</v>
       </c>
       <c r="J167" t="n">
         <v>1815373.357329</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1284.406244</v>
+        <v>1284.381541</v>
       </c>
       <c r="F168" t="n">
-        <v>1400.884168</v>
+        <v>1400.814248</v>
       </c>
       <c r="G168" t="n">
-        <v>1901.498457</v>
+        <v>1901.302653</v>
       </c>
       <c r="H168" t="n">
-        <v>2721.130745</v>
+        <v>2720.557243</v>
       </c>
       <c r="I168" t="n">
-        <v>3984.704681</v>
+        <v>3982.589329</v>
       </c>
       <c r="J168" t="n">
         <v>11152.878716</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>791731.784597</v>
+        <v>791740.134803</v>
       </c>
       <c r="F169" t="n">
-        <v>858941.29235</v>
+        <v>858962.770783</v>
       </c>
       <c r="G169" t="n">
-        <v>1159662.853897</v>
+        <v>1159718.113007</v>
       </c>
       <c r="H169" t="n">
-        <v>1704630.138283</v>
+        <v>1704785.319039</v>
       </c>
       <c r="I169" t="n">
-        <v>2603416.02304</v>
+        <v>2603982.062368</v>
       </c>
       <c r="J169" t="n">
         <v>2335967.991281</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>35704.793662</v>
+        <v>35704.763957</v>
       </c>
       <c r="F170" t="n">
-        <v>46398.585358</v>
+        <v>46398.398745</v>
       </c>
       <c r="G170" t="n">
-        <v>71665.547252</v>
+        <v>71664.734558</v>
       </c>
       <c r="H170" t="n">
-        <v>109683.192984</v>
+        <v>109680.138453</v>
       </c>
       <c r="I170" t="n">
-        <v>164997.621609</v>
+        <v>164984.59869</v>
       </c>
       <c r="J170" t="n">
         <v>268686.629292</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>76128.58841700001</v>
+        <v>76125.33909199999</v>
       </c>
       <c r="F171" t="n">
-        <v>79029.832939</v>
+        <v>79021.233112</v>
       </c>
       <c r="G171" t="n">
-        <v>102406.283822</v>
+        <v>102383.637904</v>
       </c>
       <c r="H171" t="n">
-        <v>140144.0394</v>
+        <v>140081.451071</v>
       </c>
       <c r="I171" t="n">
-        <v>196848.272492</v>
+        <v>196630.040748</v>
       </c>
       <c r="J171" t="n">
         <v>807659.335887</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>14790.232073</v>
+        <v>14780.754858</v>
       </c>
       <c r="F172" t="n">
-        <v>14451.300273</v>
+        <v>14428.421614</v>
       </c>
       <c r="G172" t="n">
-        <v>17052.451015</v>
+        <v>16999.747028</v>
       </c>
       <c r="H172" t="n">
-        <v>21821.300926</v>
+        <v>21692.970043</v>
       </c>
       <c r="I172" t="n">
-        <v>32018.037629</v>
+        <v>31608.647074</v>
       </c>
       <c r="J172" t="n">
         <v>1003841.74517</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2835.296519</v>
+        <v>2835.31402</v>
       </c>
       <c r="F173" t="n">
-        <v>3649.326112</v>
+        <v>3649.376256</v>
       </c>
       <c r="G173" t="n">
-        <v>5606.444096</v>
+        <v>5606.581967</v>
       </c>
       <c r="H173" t="n">
-        <v>8548.511193</v>
+        <v>8548.891544</v>
       </c>
       <c r="I173" t="n">
-        <v>12977.751497</v>
+        <v>12979.066033</v>
       </c>
       <c r="J173" t="n">
         <v>15381.339853</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1004126.645749</v>
+        <v>1004129.804909</v>
       </c>
       <c r="F174" t="n">
-        <v>992366.868992</v>
+        <v>992373.292951</v>
       </c>
       <c r="G174" t="n">
-        <v>1229884.001776</v>
+        <v>1229896.952748</v>
       </c>
       <c r="H174" t="n">
-        <v>1636771.38457</v>
+        <v>1636798.989665</v>
       </c>
       <c r="I174" t="n">
-        <v>2256802.903475</v>
+        <v>2256877.963038</v>
       </c>
       <c r="J174" t="n">
         <v>2898472.854082</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5876.665667</v>
+        <v>5876.739235</v>
       </c>
       <c r="F175" t="n">
-        <v>8923.177057000001</v>
+        <v>8923.441468999999</v>
       </c>
       <c r="G175" t="n">
-        <v>16164.775085</v>
+        <v>16165.686185</v>
       </c>
       <c r="H175" t="n">
-        <v>28461.813404</v>
+        <v>28464.882221</v>
       </c>
       <c r="I175" t="n">
-        <v>48315.566007</v>
+        <v>48328.050172</v>
       </c>
       <c r="J175" t="n">
         <v>40199.15992</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>502.305821</v>
+        <v>502.289304</v>
       </c>
       <c r="F176" t="n">
-        <v>467.037765</v>
+        <v>466.998699</v>
       </c>
       <c r="G176" t="n">
-        <v>561.336758</v>
+        <v>561.241341</v>
       </c>
       <c r="H176" t="n">
-        <v>734.116025</v>
+        <v>733.863563</v>
       </c>
       <c r="I176" t="n">
-        <v>1005.383046</v>
+        <v>1004.52119</v>
       </c>
       <c r="J176" t="n">
         <v>3442.027658</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>518193.653688</v>
+        <v>518193.411213</v>
       </c>
       <c r="F177" t="n">
-        <v>689346.502829</v>
+        <v>689344.265859</v>
       </c>
       <c r="G177" t="n">
-        <v>1071962.001908</v>
+        <v>1071951.303007</v>
       </c>
       <c r="H177" t="n">
-        <v>1612225.487001</v>
+        <v>1612184.699746</v>
       </c>
       <c r="I177" t="n">
-        <v>2330509.882627</v>
+        <v>2330340.983379</v>
       </c>
       <c r="J177" t="n">
         <v>3575315.571137</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1259.363406</v>
+        <v>1259.327411</v>
       </c>
       <c r="F178" t="n">
-        <v>1457.254633</v>
+        <v>1457.147375</v>
       </c>
       <c r="G178" t="n">
-        <v>2034.218234</v>
+        <v>2033.911793</v>
       </c>
       <c r="H178" t="n">
-        <v>2939.243476</v>
+        <v>2938.344328</v>
       </c>
       <c r="I178" t="n">
-        <v>4318.581119</v>
+        <v>4315.280618</v>
       </c>
       <c r="J178" t="n">
         <v>14667.069235</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>872.603311</v>
+        <v>872.580053</v>
       </c>
       <c r="F179" t="n">
-        <v>886.237794</v>
+        <v>886.177059</v>
       </c>
       <c r="G179" t="n">
-        <v>1153.138998</v>
+        <v>1152.976879</v>
       </c>
       <c r="H179" t="n">
-        <v>1570.436877</v>
+        <v>1569.987251</v>
       </c>
       <c r="I179" t="n">
-        <v>2168.273881</v>
+        <v>2166.718896</v>
       </c>
       <c r="J179" t="n">
         <v>6756.175225</v>
@@ -14130,58 +14130,58 @@
         </is>
       </c>
       <c r="E181" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="G181" t="n">
+        <v>8e-06</v>
+      </c>
+      <c r="H181" t="n">
         <v>-2e-06</v>
       </c>
-      <c r="F181" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="G181" t="n">
+      <c r="I181" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="J181" t="n">
+        <v>9e-06</v>
+      </c>
+      <c r="K181" t="n">
         <v>3e-06</v>
       </c>
-      <c r="H181" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="I181" t="n">
+      <c r="L181" t="n">
+        <v>-4e-06</v>
+      </c>
+      <c r="M181" t="n">
+        <v>-7e-06</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-3e-06</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
         <v>2e-06</v>
       </c>
-      <c r="J181" t="n">
-        <v>6e-06</v>
-      </c>
-      <c r="K181" t="n">
+      <c r="Q181" t="n">
         <v>-0</v>
-      </c>
-      <c r="L181" t="n">
-        <v>-2e-06</v>
-      </c>
-      <c r="M181" t="n">
-        <v>-4e-06</v>
-      </c>
-      <c r="N181" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="O181" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>3e-06</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
       <c r="S181" t="n">
-        <v>1e-06</v>
+        <v>2e-06</v>
       </c>
       <c r="T181" t="n">
-        <v>-3e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="U181" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="V181" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
